--- a/results_curated/synapse_table.xlsx
+++ b/results_curated/synapse_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,6 +571,11 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>N_Unclear_Cells</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Clipped_Z</t>
         </is>
       </c>
@@ -596,7 +601,7 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
         <v>114.1761741364326</v>
@@ -664,7 +669,10 @@
       <c r="AB2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" t="b">
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -686,64 +694,64 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>168.6503586615303</v>
+        <v>154.0459302428013</v>
       </c>
       <c r="H3" t="n">
-        <v>14.65374716178864</v>
+        <v>14.00490521533969</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3060055285838987</v>
+        <v>0.1065723238586391</v>
       </c>
       <c r="J3" t="n">
-        <v>1.689020365701372</v>
+        <v>2.228445393677191</v>
       </c>
       <c r="K3" t="n">
-        <v>173.1552470835068</v>
+        <v>120.8617085624804</v>
       </c>
       <c r="L3" t="n">
-        <v>14.21156786870511</v>
+        <v>16.15593092198533</v>
       </c>
       <c r="M3" t="n">
-        <v>10.442294886781</v>
+        <v>9.38438570100233</v>
       </c>
       <c r="N3" t="n">
-        <v>551.1350054425268</v>
+        <v>1445.459052268886</v>
       </c>
       <c r="O3" t="n">
-        <v>521.5946126338606</v>
+        <v>1753.373932142347</v>
       </c>
       <c r="P3" t="n">
-        <v>1343.905487459413</v>
+        <v>728.6631621247608</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.3971405029297</v>
+        <v>65.76412963867188</v>
       </c>
       <c r="R3" t="n">
-        <v>528.5255737304688</v>
+        <v>113.3885498046875</v>
       </c>
       <c r="S3" t="n">
-        <v>7.111623616236162</v>
+        <v>11.50907205806117</v>
       </c>
       <c r="T3" t="n">
-        <v>10.5721435546875</v>
+        <v>24.0405158996582</v>
       </c>
       <c r="U3" t="n">
-        <v>6.259334564208984</v>
+        <v>10.78802108764648</v>
       </c>
       <c r="V3" t="n">
-        <v>7.06005859375</v>
+        <v>14.443603515625</v>
       </c>
       <c r="W3" t="n">
         <v>35</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6802777823979073</v>
+        <v>1.391725357370585</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
@@ -752,12 +760,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC3" t="b">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -779,64 +790,64 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>154.0459302428013</v>
+        <v>109.4762768709988</v>
       </c>
       <c r="H4" t="n">
-        <v>14.00490521533969</v>
+        <v>11.80633410176635</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1065723238586391</v>
+        <v>0.08424455865445027</v>
       </c>
       <c r="J4" t="n">
-        <v>2.228445393677191</v>
+        <v>1.033815198702482</v>
       </c>
       <c r="K4" t="n">
-        <v>120.8617085624804</v>
+        <v>92.64909519071573</v>
       </c>
       <c r="L4" t="n">
-        <v>16.15593092198533</v>
+        <v>13.42001339626892</v>
       </c>
       <c r="M4" t="n">
-        <v>9.38438570100233</v>
+        <v>11.51347801753845</v>
       </c>
       <c r="N4" t="n">
-        <v>1445.459052268886</v>
+        <v>1299.505613413474</v>
       </c>
       <c r="O4" t="n">
-        <v>1753.373932142347</v>
+        <v>1433.159172584801</v>
       </c>
       <c r="P4" t="n">
-        <v>728.6631621247608</v>
+        <v>1196.784028461521</v>
       </c>
       <c r="Q4" t="n">
-        <v>65.76412963867188</v>
+        <v>54.5325813293457</v>
       </c>
       <c r="R4" t="n">
-        <v>113.3885498046875</v>
+        <v>132.9365997314453</v>
       </c>
       <c r="S4" t="n">
-        <v>11.50907205806117</v>
+        <v>11.11555169417898</v>
       </c>
       <c r="T4" t="n">
-        <v>24.0405158996582</v>
+        <v>16.26449966430664</v>
       </c>
       <c r="U4" t="n">
-        <v>10.78802108764648</v>
+        <v>15.73250198364258</v>
       </c>
       <c r="V4" t="n">
-        <v>14.443603515625</v>
+        <v>15.788330078125</v>
       </c>
       <c r="W4" t="n">
         <v>35</v>
       </c>
       <c r="X4" t="n">
-        <v>1.391725357370585</v>
+        <v>1.521297596994615</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
@@ -845,12 +856,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC4" t="b">
+        <v>2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -872,64 +886,64 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>109.4762768709988</v>
+        <v>90.30862930663058</v>
       </c>
       <c r="H5" t="n">
-        <v>11.80633410176635</v>
+        <v>10.72308342148054</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08424455865445027</v>
+        <v>0.06919946225118713</v>
       </c>
       <c r="J5" t="n">
-        <v>1.033815198702482</v>
+        <v>2.113641751452312</v>
       </c>
       <c r="K5" t="n">
-        <v>92.64909519071573</v>
+        <v>69.06710728928616</v>
       </c>
       <c r="L5" t="n">
-        <v>13.42001339626892</v>
+        <v>9.507918165045773</v>
       </c>
       <c r="M5" t="n">
-        <v>11.51347801753845</v>
+        <v>9.085066202002274</v>
       </c>
       <c r="N5" t="n">
-        <v>1299.505613413474</v>
+        <v>1305.048137206895</v>
       </c>
       <c r="O5" t="n">
-        <v>1433.159172584801</v>
+        <v>1234.525586743114</v>
       </c>
       <c r="P5" t="n">
         <v>1196.784028461521</v>
       </c>
       <c r="Q5" t="n">
-        <v>54.5325813293457</v>
+        <v>63.72148513793945</v>
       </c>
       <c r="R5" t="n">
-        <v>132.9365997314453</v>
+        <v>86.38650512695312</v>
       </c>
       <c r="S5" t="n">
-        <v>11.11555169417898</v>
+        <v>7.326259946949602</v>
       </c>
       <c r="T5" t="n">
-        <v>16.26449966430664</v>
+        <v>30.64437866210938</v>
       </c>
       <c r="U5" t="n">
-        <v>15.73250198364258</v>
+        <v>14.49837875366211</v>
       </c>
       <c r="V5" t="n">
-        <v>15.788330078125</v>
+        <v>15.78958129882812</v>
       </c>
       <c r="W5" t="n">
         <v>35</v>
       </c>
       <c r="X5" t="n">
-        <v>1.521297596994615</v>
+        <v>1.521418159399857</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
@@ -938,19 +952,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC5" t="b">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4_stack2</t>
+          <t>4_stack3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -959,70 +976,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>90.30862930663058</v>
+        <v>15.8949164610191</v>
       </c>
       <c r="H6" t="n">
-        <v>10.72308342148054</v>
+        <v>4.498670492315635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06919946225118713</v>
+        <v>0.02836049955572677</v>
       </c>
       <c r="J6" t="n">
-        <v>2.113641751452312</v>
+        <v>0.1690499108048101</v>
       </c>
       <c r="K6" t="n">
-        <v>69.06710728928616</v>
+        <v>14.45350319710268</v>
       </c>
       <c r="L6" t="n">
-        <v>9.507918165045773</v>
+        <v>7.047081171319082</v>
       </c>
       <c r="M6" t="n">
-        <v>9.085066202002274</v>
+        <v>2.186170006727887</v>
       </c>
       <c r="N6" t="n">
-        <v>1305.048137206895</v>
+        <v>560.4596784265556</v>
       </c>
       <c r="O6" t="n">
-        <v>1234.525586743114</v>
+        <v>697.3557156500093</v>
       </c>
       <c r="P6" t="n">
-        <v>1196.784028461521</v>
+        <v>425.5929565891027</v>
       </c>
       <c r="Q6" t="n">
-        <v>63.72148513793945</v>
+        <v>126.139533996582</v>
       </c>
       <c r="R6" t="n">
-        <v>86.38650512695312</v>
+        <v>62.81967163085938</v>
       </c>
       <c r="S6" t="n">
-        <v>7.326259946949602</v>
+        <v>6.364341085271318</v>
       </c>
       <c r="T6" t="n">
-        <v>30.64437866210938</v>
+        <v>2.261157989501953</v>
       </c>
       <c r="U6" t="n">
-        <v>14.49837875366211</v>
+        <v>13.37568283081055</v>
       </c>
       <c r="V6" t="n">
-        <v>15.78958129882812</v>
+        <v>12.9637336730957</v>
       </c>
       <c r="W6" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="X6" t="n">
-        <v>1.521418159399857</v>
+        <v>1.24913127527549</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
@@ -1031,19 +1048,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA6" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AB6" t="n">
         <v>3</v>
       </c>
-      <c r="AC6" t="b">
-        <v>0</v>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4_stack2</t>
+          <t>4_stack3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1052,7 +1072,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -1061,61 +1081,61 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>46.91815452177602</v>
+        <v>11.63438836352713</v>
       </c>
       <c r="H7" t="n">
-        <v>7.729039377770055</v>
+        <v>3.848813238291689</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02823110707235843</v>
+        <v>0.01302891389900827</v>
       </c>
       <c r="J7" t="n">
-        <v>2.014930270526772</v>
+        <v>0.4041330323201041</v>
       </c>
       <c r="K7" t="n">
-        <v>50.22792161252885</v>
+        <v>11.80392608584911</v>
       </c>
       <c r="L7" t="n">
-        <v>8.23046612105386</v>
+        <v>4.894754354559324</v>
       </c>
       <c r="M7" t="n">
-        <v>8.097557570469693</v>
+        <v>3.481432189742025</v>
       </c>
       <c r="N7" t="n">
-        <v>1661.931089047316</v>
+        <v>892.9668622963814</v>
       </c>
       <c r="O7" t="n">
-        <v>2482.233256212438</v>
+        <v>1094.779816889649</v>
       </c>
       <c r="P7" t="n">
-        <v>1343.905487459413</v>
+        <v>425.5929565891027</v>
       </c>
       <c r="Q7" t="n">
-        <v>75.59008026123047</v>
+        <v>100.6464614868164</v>
       </c>
       <c r="R7" t="n">
-        <v>191.2167663574219</v>
+        <v>231.3558349609375</v>
       </c>
       <c r="S7" t="n">
-        <v>5.691906005221932</v>
+        <v>5.363636363636363</v>
       </c>
       <c r="T7" t="n">
-        <v>13.49282455444336</v>
+        <v>5.348232269287109</v>
       </c>
       <c r="U7" t="n">
-        <v>6.696422576904297</v>
+        <v>13.23384094238281</v>
       </c>
       <c r="V7" t="n">
-        <v>7.058490753173828</v>
+        <v>12.97411727905273</v>
       </c>
       <c r="W7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="X7" t="n">
-        <v>0.680126711823046</v>
+        <v>1.250131796211676</v>
       </c>
       <c r="Y7" t="n">
         <v>1</v>
@@ -1124,12 +1144,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AB7" t="n">
         <v>3</v>
       </c>
-      <c r="AC7" t="b">
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1145,70 +1168,66 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>128.3093020632571</v>
+        <v>0.8403261435933991</v>
       </c>
       <c r="H8" t="n">
-        <v>12.78156787504209</v>
+        <v>1.034377337579432</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2356699363748929</v>
+        <v>0.0009410496392132517</v>
       </c>
       <c r="J8" t="n">
-        <v>1.481623031094765</v>
+        <v>0.3550025789396508</v>
       </c>
       <c r="K8" t="n">
-        <v>135.7827213399805</v>
-      </c>
-      <c r="L8" t="n">
-        <v>10.68883565236174</v>
-      </c>
-      <c r="M8" t="n">
-        <v>10.3547573162643</v>
-      </c>
+        <v>0.0392323890661046</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>544.4449302143851</v>
+        <v>892.9668622963814</v>
       </c>
       <c r="O8" t="n">
-        <v>568.2026908443929</v>
+        <v>1094.779816889649</v>
       </c>
       <c r="P8" t="n">
-        <v>273.5674489579474</v>
+        <v>13.45670944967388</v>
       </c>
       <c r="Q8" t="n">
-        <v>76.83366394042969</v>
+        <v>26</v>
       </c>
       <c r="R8" t="n">
-        <v>281.5971374511719</v>
+        <v>231.3558349609375</v>
       </c>
       <c r="S8" t="n">
-        <v>6.460569913850232</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>10.86809921264648</v>
+        <v>5.282608032226562</v>
       </c>
       <c r="U8" t="n">
-        <v>7.33526611328125</v>
+        <v>14.88047790527344</v>
       </c>
       <c r="V8" t="n">
-        <v>9.001178741455078</v>
+        <v>14.32791137695312</v>
       </c>
       <c r="W8" t="n">
         <v>30</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8673160189668923</v>
+        <v>1.380577745705401</v>
       </c>
       <c r="Y8" t="n">
         <v>1</v>
@@ -1217,19 +1236,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA8" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AB8" t="n">
         <v>3</v>
       </c>
-      <c r="AC8" t="b">
-        <v>0</v>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4_stack3</t>
+          <t>4_stack4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1238,70 +1260,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>39.91425626190949</v>
+        <v>127.2899743282249</v>
       </c>
       <c r="H9" t="n">
-        <v>7.128843487646243</v>
+        <v>12.7306963267144</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07121699882847143</v>
+        <v>0.273399039644722</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5076995416180615</v>
+        <v>0.8963547013912997</v>
       </c>
       <c r="K9" t="n">
-        <v>42.72515244122326</v>
+        <v>137.4370828418535</v>
       </c>
       <c r="L9" t="n">
-        <v>8.126626001611559</v>
+        <v>10.62450949569433</v>
       </c>
       <c r="M9" t="n">
-        <v>5.290281704453182</v>
+        <v>9.94432886255986</v>
       </c>
       <c r="N9" t="n">
-        <v>560.4596784265556</v>
+        <v>465.5831069986066</v>
       </c>
       <c r="O9" t="n">
-        <v>697.3557156500093</v>
+        <v>379.0633431567027</v>
       </c>
       <c r="P9" t="n">
-        <v>666.2051987315223</v>
+        <v>241.8284462034688</v>
       </c>
       <c r="Q9" t="n">
-        <v>103.8786163330078</v>
+        <v>99.44197082519531</v>
       </c>
       <c r="R9" t="n">
-        <v>62.81967163085938</v>
+        <v>507.7198486328125</v>
       </c>
       <c r="S9" t="n">
-        <v>5.699421965317919</v>
+        <v>4.649500384319754</v>
       </c>
       <c r="T9" t="n">
-        <v>7.10919189453125</v>
+        <v>13.88815689086914</v>
       </c>
       <c r="U9" t="n">
-        <v>14.00275421142578</v>
+        <v>15.49404144287109</v>
       </c>
       <c r="V9" t="n">
-        <v>13.42066955566406</v>
+        <v>14.84336471557617</v>
       </c>
       <c r="W9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X9" t="n">
-        <v>1.29315970999228</v>
+        <v>1.430244678277108</v>
       </c>
       <c r="Y9" t="n">
         <v>1</v>
@@ -1310,19 +1332,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC9" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4_stack3</t>
+          <t>4_stack4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1331,70 +1356,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>13.65072976428794</v>
+        <v>125.0300324168325</v>
       </c>
       <c r="H10" t="n">
-        <v>4.169010548125864</v>
+        <v>12.61717803443506</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01528693878872873</v>
+        <v>0.1066699651519417</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4689521982421185</v>
+        <v>0.9211407866048004</v>
       </c>
       <c r="K10" t="n">
-        <v>13.58657117513482</v>
+        <v>129.0109616782029</v>
       </c>
       <c r="L10" t="n">
-        <v>4.663425714079618</v>
+        <v>11.97755813991224</v>
       </c>
       <c r="M10" t="n">
-        <v>3.436966290089467</v>
+        <v>9.528278826371544</v>
       </c>
       <c r="N10" t="n">
-        <v>892.9668622963814</v>
+        <v>1172.120308080523</v>
       </c>
       <c r="O10" t="n">
-        <v>1094.779816889649</v>
+        <v>1537.752721835036</v>
       </c>
       <c r="P10" t="n">
-        <v>666.2051987315223</v>
+        <v>1128.755065820895</v>
       </c>
       <c r="Q10" t="n">
-        <v>95.54701232910156</v>
+        <v>75.88176727294922</v>
       </c>
       <c r="R10" t="n">
-        <v>231.3558349609375</v>
+        <v>155.4335327148438</v>
       </c>
       <c r="S10" t="n">
-        <v>5.461538461538462</v>
+        <v>5.756410256410256</v>
       </c>
       <c r="T10" t="n">
-        <v>6.430335998535156</v>
+        <v>13.52622985839844</v>
       </c>
       <c r="U10" t="n">
-        <v>13.71213531494141</v>
+        <v>14.6842155456543</v>
       </c>
       <c r="V10" t="n">
-        <v>13.4378547668457</v>
+        <v>14.51008605957031</v>
       </c>
       <c r="W10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
-        <v>1.294815605222815</v>
+        <v>1.398131337853995</v>
       </c>
       <c r="Y10" t="n">
         <v>1</v>
@@ -1403,12 +1428,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA10" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC10" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1424,70 +1452,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>125.0300324168325</v>
+        <v>109.4453161680711</v>
       </c>
       <c r="H11" t="n">
-        <v>12.61717803443506</v>
+        <v>11.80466452429847</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1066699651519417</v>
+        <v>0.06900596659355307</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9211407866048004</v>
+        <v>0.5376505284492288</v>
       </c>
       <c r="K11" t="n">
-        <v>129.0109616782029</v>
+        <v>102.029289843424</v>
       </c>
       <c r="L11" t="n">
-        <v>11.97755813991224</v>
+        <v>12.05752385490945</v>
       </c>
       <c r="M11" t="n">
-        <v>9.528278826371544</v>
+        <v>9.850651903221857</v>
       </c>
       <c r="N11" t="n">
-        <v>1172.120308080523</v>
+        <v>1586.026854934252</v>
       </c>
       <c r="O11" t="n">
-        <v>1537.752721835036</v>
+        <v>2577.057940585213</v>
       </c>
       <c r="P11" t="n">
-        <v>1128.755065820895</v>
+        <v>577.4223022749275</v>
       </c>
       <c r="Q11" t="n">
-        <v>75.88176727294922</v>
+        <v>67.776611328125</v>
       </c>
       <c r="R11" t="n">
-        <v>155.4335327148438</v>
+        <v>67.20449829101562</v>
       </c>
       <c r="S11" t="n">
-        <v>5.756410256410256</v>
+        <v>9.729032258064516</v>
       </c>
       <c r="T11" t="n">
-        <v>13.52622985839844</v>
+        <v>14.99295425415039</v>
       </c>
       <c r="U11" t="n">
-        <v>14.6842155456543</v>
+        <v>27.88605880737305</v>
       </c>
       <c r="V11" t="n">
-        <v>14.51008605957031</v>
+        <v>24.94808197021484</v>
       </c>
       <c r="W11" t="n">
         <v>31</v>
       </c>
       <c r="X11" t="n">
-        <v>1.398131337853995</v>
+        <v>2.403893062984392</v>
       </c>
       <c r="Y11" t="n">
         <v>1</v>
@@ -1496,12 +1524,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA11" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC11" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1517,70 +1548,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>109.4453161680711</v>
+        <v>86.45332996913211</v>
       </c>
       <c r="H12" t="n">
-        <v>11.80466452429847</v>
+        <v>10.49170141067389</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06836866236261323</v>
+        <v>0.05501616956115146</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5411217731299777</v>
+        <v>1.37181368965013</v>
       </c>
       <c r="K12" t="n">
-        <v>102.029289843424</v>
+        <v>96.20068565728113</v>
       </c>
       <c r="L12" t="n">
-        <v>12.05752385490945</v>
+        <v>10.01098328902463</v>
       </c>
       <c r="M12" t="n">
-        <v>9.850651903221857</v>
+        <v>9.905425277287478</v>
       </c>
       <c r="N12" t="n">
-        <v>1600.811137529586</v>
+        <v>1571.416742727566</v>
       </c>
       <c r="O12" t="n">
-        <v>2575.410180244437</v>
+        <v>2035.219415193242</v>
       </c>
       <c r="P12" t="n">
-        <v>578.756203503175</v>
+        <v>755.9689049147695</v>
       </c>
       <c r="Q12" t="n">
-        <v>67.776611328125</v>
+        <v>80.64914703369141</v>
       </c>
       <c r="R12" t="n">
-        <v>77.89161682128906</v>
+        <v>68.82208251953125</v>
       </c>
       <c r="S12" t="n">
-        <v>9.729032258064516</v>
+        <v>5.340341655716163</v>
       </c>
       <c r="T12" t="n">
-        <v>14.99295425415039</v>
+        <v>18.9671516418457</v>
       </c>
       <c r="U12" t="n">
-        <v>27.70717239379883</v>
+        <v>13.82633209228516</v>
       </c>
       <c r="V12" t="n">
-        <v>24.81557083129883</v>
+        <v>14.73222351074219</v>
       </c>
       <c r="W12" t="n">
         <v>31</v>
       </c>
       <c r="X12" t="n">
-        <v>2.391124842646304</v>
+        <v>1.419535575604161</v>
       </c>
       <c r="Y12" t="n">
         <v>1</v>
@@ -1589,13 +1620,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AB12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC12" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1610,70 +1644,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>86.70414988348129</v>
+        <v>59.89629561824202</v>
       </c>
       <c r="H13" t="n">
-        <v>10.50690974189333</v>
+        <v>8.732830707410582</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04187912692227796</v>
+        <v>0.03776499460390599</v>
       </c>
       <c r="J13" t="n">
-        <v>1.37181368965013</v>
+        <v>1.881899064266573</v>
       </c>
       <c r="K13" t="n">
-        <v>96.20068565728113</v>
+        <v>56.1242383599852</v>
       </c>
       <c r="L13" t="n">
-        <v>10.01098328902463</v>
+        <v>9.438879133766743</v>
       </c>
       <c r="M13" t="n">
-        <v>9.905425277287478</v>
+        <v>7.462301537271731</v>
       </c>
       <c r="N13" t="n">
-        <v>2070.34282363127</v>
+        <v>1586.026854934252</v>
       </c>
       <c r="O13" t="n">
-        <v>2674.001173967557</v>
+        <v>2577.057940585213</v>
       </c>
       <c r="P13" t="n">
-        <v>755.9689049147695</v>
+        <v>1050.682611579347</v>
       </c>
       <c r="Q13" t="n">
-        <v>80.64914703369141</v>
+        <v>108.3254318237305</v>
       </c>
       <c r="R13" t="n">
-        <v>68.82208251953125</v>
+        <v>67.20449829101562</v>
       </c>
       <c r="S13" t="n">
-        <v>5.340341655716163</v>
+        <v>4.407582938388626</v>
       </c>
       <c r="T13" t="n">
-        <v>18.9671516418457</v>
+        <v>31.06975555419922</v>
       </c>
       <c r="U13" t="n">
-        <v>13.82633209228516</v>
+        <v>16.50978851318359</v>
       </c>
       <c r="V13" t="n">
-        <v>14.73222351074219</v>
+        <v>17.81054306030273</v>
       </c>
       <c r="W13" t="n">
         <v>31</v>
       </c>
       <c r="X13" t="n">
-        <v>1.419535575604161</v>
+        <v>1.716149600669195</v>
       </c>
       <c r="Y13" t="n">
         <v>1</v>
@@ -1682,12 +1716,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA13" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC13" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1703,70 +1740,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>59.33059619811137</v>
+        <v>19.97545702825644</v>
       </c>
       <c r="H14" t="n">
-        <v>8.691493616873288</v>
+        <v>5.04316783505507</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03706283321446147</v>
+        <v>0.02784903377848601</v>
       </c>
       <c r="J14" t="n">
-        <v>1.499659275055896</v>
+        <v>1.676359155298498</v>
       </c>
       <c r="K14" t="n">
-        <v>56.1242383599852</v>
+        <v>16.53663928011978</v>
       </c>
       <c r="L14" t="n">
-        <v>9.438879133766745</v>
+        <v>6.785105990296142</v>
       </c>
       <c r="M14" t="n">
-        <v>7.462301537271734</v>
+        <v>4.036518207166173</v>
       </c>
       <c r="N14" t="n">
-        <v>1600.811137529586</v>
+        <v>717.2764838860558</v>
       </c>
       <c r="O14" t="n">
-        <v>2575.410180244437</v>
+        <v>522.4184928042489</v>
       </c>
       <c r="P14" t="n">
-        <v>1565.60771807197</v>
+        <v>1050.682611579347</v>
       </c>
       <c r="Q14" t="n">
-        <v>108.3254318237305</v>
+        <v>66.16860198974609</v>
       </c>
       <c r="R14" t="n">
-        <v>77.89161682128906</v>
+        <v>81.94057464599609</v>
       </c>
       <c r="S14" t="n">
-        <v>4.407582938388626</v>
+        <v>5.552325581395348</v>
       </c>
       <c r="T14" t="n">
-        <v>31.06975555419922</v>
+        <v>29.17454147338867</v>
       </c>
       <c r="U14" t="n">
-        <v>20.71787643432617</v>
+        <v>17.40351486206055</v>
       </c>
       <c r="V14" t="n">
-        <v>21.26691818237305</v>
+        <v>17.8115348815918</v>
       </c>
       <c r="W14" t="n">
         <v>31</v>
       </c>
       <c r="X14" t="n">
-        <v>2.049191482964449</v>
+        <v>1.716245168429448</v>
       </c>
       <c r="Y14" t="n">
         <v>1</v>
@@ -1775,12 +1812,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA14" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AB14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC14" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1796,70 +1836,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>1.633144730635331</v>
+        <v>7.987734835476489</v>
       </c>
       <c r="H15" t="n">
-        <v>1.442007091980049</v>
+        <v>3.189090758411758</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001769299716645411</v>
+        <v>0.1817501951788347</v>
       </c>
       <c r="J15" t="n">
-        <v>2.526568710628708</v>
+        <v>1.5137126200481</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7922867063492064</v>
+        <v>7.481762127481021</v>
       </c>
       <c r="L15" t="n">
-        <v>0.594215029761905</v>
+        <v>3.052884633994278</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1980716765873023</v>
+        <v>2.15745605553137</v>
       </c>
       <c r="N15" t="n">
-        <v>923.0458329195744</v>
+        <v>43.94897528234777</v>
       </c>
       <c r="O15" t="n">
-        <v>1112.709018692859</v>
+        <v>19.65542692211841</v>
       </c>
       <c r="P15" t="n">
-        <v>755.9689049147695</v>
+        <v>577.4223022749275</v>
       </c>
       <c r="Q15" t="n">
-        <v>43.5</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="R15" t="n">
-        <v>210.3353729248047</v>
+        <v>58.71165466308594</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>13.28333333333333</v>
       </c>
       <c r="T15" t="n">
-        <v>37</v>
+        <v>37.37096405029297</v>
       </c>
       <c r="U15" t="n">
-        <v>14.64436721801758</v>
+        <v>24.68828201293945</v>
       </c>
       <c r="V15" t="n">
-        <v>14.74147796630859</v>
+        <v>24.95135498046875</v>
       </c>
       <c r="W15" t="n">
         <v>31</v>
       </c>
       <c r="X15" t="n">
-        <v>1.420427296320981</v>
+        <v>2.404208436593226</v>
       </c>
       <c r="Y15" t="n">
         <v>1</v>
@@ -1868,19 +1908,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AB15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC15" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4_stack5</t>
+          <t>4_stack4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1889,70 +1932,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>118.4499575301748</v>
+        <v>4.563614721608481</v>
       </c>
       <c r="H16" t="n">
-        <v>12.28068279859142</v>
+        <v>2.41051337488251</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2449504851779369</v>
+        <v>0.006362420662230217</v>
       </c>
       <c r="J16" t="n">
-        <v>1.389294897395971</v>
+        <v>1.944422084928604</v>
       </c>
       <c r="K16" t="n">
-        <v>128.6071794000012</v>
+        <v>2.690719231576456</v>
       </c>
       <c r="L16" t="n">
-        <v>11.43713085362248</v>
+        <v>6.869940981436477</v>
       </c>
       <c r="M16" t="n">
-        <v>9.677074743983724</v>
+        <v>3.912494419215482</v>
       </c>
       <c r="N16" t="n">
-        <v>483.5669439239134</v>
+        <v>717.2764838860558</v>
       </c>
       <c r="O16" t="n">
-        <v>438.5788773699833</v>
+        <v>522.4184928042489</v>
       </c>
       <c r="P16" t="n">
-        <v>225.8216314644981</v>
+        <v>1128.755065820895</v>
       </c>
       <c r="Q16" t="n">
-        <v>139.2848205566406</v>
+        <v>56.40740585327148</v>
       </c>
       <c r="R16" t="n">
-        <v>428.4662475585938</v>
+        <v>81.94057464599609</v>
       </c>
       <c r="S16" t="n">
-        <v>5.395862068965517</v>
+        <v>7.25925925925926</v>
       </c>
       <c r="T16" t="n">
-        <v>11.81031036376953</v>
+        <v>27.95769119262695</v>
       </c>
       <c r="U16" t="n">
-        <v>8.500938415527344</v>
+        <v>14.3784065246582</v>
       </c>
       <c r="V16" t="n">
-        <v>10.03471374511719</v>
+        <v>14.52207565307617</v>
       </c>
       <c r="W16" t="n">
         <v>31</v>
       </c>
       <c r="X16" t="n">
-        <v>0.9669031386749769</v>
+        <v>1.399286605048128</v>
       </c>
       <c r="Y16" t="n">
         <v>1</v>
@@ -1961,19 +2004,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA16" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AB16" t="n">
         <v>5</v>
       </c>
-      <c r="AC16" t="b">
-        <v>0</v>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4_stack5</t>
+          <t>4_stack4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1982,70 +2028,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>106.1975072772838</v>
+        <v>1.633144730635331</v>
       </c>
       <c r="H17" t="n">
-        <v>11.62819271502403</v>
+        <v>1.442007091980049</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1172627293234258</v>
+        <v>0.001769299716645411</v>
       </c>
       <c r="J17" t="n">
-        <v>2.605195175123174</v>
+        <v>2.526568710628708</v>
       </c>
       <c r="K17" t="n">
-        <v>121.5358007118185</v>
+        <v>0.7922867063492064</v>
       </c>
       <c r="L17" t="n">
-        <v>12.27364780845073</v>
+        <v>0.594215029761905</v>
       </c>
       <c r="M17" t="n">
-        <v>7.615209127594911</v>
+        <v>0.1980716765873023</v>
       </c>
       <c r="N17" t="n">
-        <v>905.6373486274343</v>
+        <v>923.0458329195744</v>
       </c>
       <c r="O17" t="n">
-        <v>1058.293695058172</v>
+        <v>1112.709018692859</v>
       </c>
       <c r="P17" t="n">
-        <v>487.4232017572836</v>
+        <v>755.9689049147695</v>
       </c>
       <c r="Q17" t="n">
-        <v>90.135986328125</v>
+        <v>43.5</v>
       </c>
       <c r="R17" t="n">
-        <v>65.54805755615234</v>
+        <v>210.3353729248047</v>
       </c>
       <c r="S17" t="n">
-        <v>6.682701202590194</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>28.19053649902344</v>
+        <v>37</v>
       </c>
       <c r="U17" t="n">
-        <v>10.82089233398438</v>
+        <v>14.64436721801758</v>
       </c>
       <c r="V17" t="n">
-        <v>15.38671112060547</v>
+        <v>14.74147796630859</v>
       </c>
       <c r="W17" t="n">
         <v>31</v>
       </c>
       <c r="X17" t="n">
-        <v>1.482599270321772</v>
+        <v>1.420427296320981</v>
       </c>
       <c r="Y17" t="n">
         <v>1</v>
@@ -2054,12 +2100,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA17" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="AB17" t="n">
         <v>5</v>
       </c>
-      <c r="AC17" t="b">
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2075,7 +2124,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
@@ -2084,61 +2133,61 @@
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>69.3218691065797</v>
+        <v>152.9956515212857</v>
       </c>
       <c r="H18" t="n">
-        <v>9.394857373129838</v>
+        <v>13.95708113071717</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05006765981574318</v>
+        <v>0.1725438785092355</v>
       </c>
       <c r="J18" t="n">
-        <v>2.02247252287449</v>
+        <v>1.246788403486755</v>
       </c>
       <c r="K18" t="n">
-        <v>67.80370032093514</v>
+        <v>152.1825661403342</v>
       </c>
       <c r="L18" t="n">
-        <v>12.68237279552371</v>
+        <v>14.56128258406767</v>
       </c>
       <c r="M18" t="n">
-        <v>7.105037907385942</v>
+        <v>11.68019906978114</v>
       </c>
       <c r="N18" t="n">
-        <v>1384.563795505822</v>
+        <v>886.7057634449575</v>
       </c>
       <c r="O18" t="n">
-        <v>2562.659653797953</v>
+        <v>960.0165604475795</v>
       </c>
       <c r="P18" t="n">
-        <v>491.9741588889517</v>
+        <v>1637.01066617228</v>
       </c>
       <c r="Q18" t="n">
-        <v>107.2456130981445</v>
+        <v>75.25598907470703</v>
       </c>
       <c r="R18" t="n">
-        <v>120.372184753418</v>
+        <v>116.9222869873047</v>
       </c>
       <c r="S18" t="n">
-        <v>5.988304093567251</v>
+        <v>6.877264757451782</v>
       </c>
       <c r="T18" t="n">
-        <v>16.41038513183594</v>
+        <v>22.43595123291016</v>
       </c>
       <c r="U18" t="n">
-        <v>8.114021301269531</v>
+        <v>17.9949951171875</v>
       </c>
       <c r="V18" t="n">
-        <v>9.773429870605469</v>
+        <v>18.61393356323242</v>
       </c>
       <c r="W18" t="n">
         <v>31</v>
       </c>
       <c r="X18" t="n">
-        <v>0.9417269149412933</v>
+        <v>1.793560956747226</v>
       </c>
       <c r="Y18" t="n">
         <v>1</v>
@@ -2147,13 +2196,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC18" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2168,70 +2220,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>52.70558494055894</v>
+        <v>94.39263442991603</v>
       </c>
       <c r="H19" t="n">
-        <v>8.191876157188762</v>
+        <v>10.96286618033345</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0587547334429005</v>
+        <v>0.1969755860611815</v>
       </c>
       <c r="J19" t="n">
-        <v>1.466843574006003</v>
+        <v>1.041118455760119</v>
       </c>
       <c r="K19" t="n">
-        <v>41.18466864403504</v>
+        <v>103.4892333346189</v>
       </c>
       <c r="L19" t="n">
-        <v>9.960359777506802</v>
+        <v>13.20751885662731</v>
       </c>
       <c r="M19" t="n">
-        <v>9.627030526182134</v>
+        <v>5.74225388186712</v>
       </c>
       <c r="N19" t="n">
-        <v>897.0440652544139</v>
+        <v>479.2098163911402</v>
       </c>
       <c r="O19" t="n">
-        <v>1033.381128001195</v>
+        <v>402.7204737635637</v>
       </c>
       <c r="P19" t="n">
-        <v>1795.901841890004</v>
+        <v>84.70272799371983</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.702880859375</v>
+        <v>106.6652297973633</v>
       </c>
       <c r="R19" t="n">
-        <v>71.33538055419922</v>
+        <v>276.4703369140625</v>
       </c>
       <c r="S19" t="n">
-        <v>7.206208425720621</v>
+        <v>6.823466092572659</v>
       </c>
       <c r="T19" t="n">
-        <v>23.89323806762695</v>
+        <v>15.24468612670898</v>
       </c>
       <c r="U19" t="n">
-        <v>16.28887939453125</v>
+        <v>14.64260482788086</v>
       </c>
       <c r="V19" t="n">
-        <v>16.69562911987305</v>
+        <v>15.02714157104492</v>
       </c>
       <c r="W19" t="n">
         <v>31</v>
       </c>
       <c r="X19" t="n">
-        <v>1.608721146232365</v>
+        <v>1.447952649115341</v>
       </c>
       <c r="Y19" t="n">
         <v>1</v>
@@ -2240,13 +2292,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC19" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2261,70 +2316,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>22.7130017499178</v>
+        <v>52.70558494055894</v>
       </c>
       <c r="H20" t="n">
-        <v>5.377647441738282</v>
+        <v>8.191876157188762</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02851838036137732</v>
+        <v>0.0587547334429005</v>
       </c>
       <c r="J20" t="n">
-        <v>1.258838206046416</v>
+        <v>1.466843574006003</v>
       </c>
       <c r="K20" t="n">
-        <v>13.0555430734509</v>
+        <v>41.18466864403504</v>
       </c>
       <c r="L20" t="n">
-        <v>8.638549078242617</v>
+        <v>9.960359777506802</v>
       </c>
       <c r="M20" t="n">
-        <v>5.225477306731772</v>
+        <v>9.627030526182134</v>
       </c>
       <c r="N20" t="n">
-        <v>796.4337897911694</v>
+        <v>897.0440652544139</v>
       </c>
       <c r="O20" t="n">
-        <v>909.2498489960402</v>
+        <v>1033.381128001195</v>
       </c>
       <c r="P20" t="n">
         <v>1795.901841890004</v>
       </c>
       <c r="Q20" t="n">
-        <v>93.84137725830078</v>
+        <v>58.702880859375</v>
       </c>
       <c r="R20" t="n">
-        <v>55.63848495483398</v>
+        <v>71.33538055419922</v>
       </c>
       <c r="S20" t="n">
-        <v>5.310344827586207</v>
+        <v>7.206208425720621</v>
       </c>
       <c r="T20" t="n">
-        <v>20.87104034423828</v>
+        <v>23.89323806762695</v>
       </c>
       <c r="U20" t="n">
-        <v>16.57960510253906</v>
+        <v>16.28887939453125</v>
       </c>
       <c r="V20" t="n">
-        <v>16.69301223754883</v>
+        <v>16.69562911987305</v>
       </c>
       <c r="W20" t="n">
         <v>31</v>
       </c>
       <c r="X20" t="n">
-        <v>1.608468994372621</v>
+        <v>1.608721146232365</v>
       </c>
       <c r="Y20" t="n">
         <v>1</v>
@@ -2333,12 +2388,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC20" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2354,70 +2412,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>12.48880429447049</v>
+        <v>31.03686043335685</v>
       </c>
       <c r="H21" t="n">
-        <v>3.987635827677616</v>
+        <v>6.286283325477469</v>
       </c>
       <c r="I21" t="n">
-        <v>0.009697216454709509</v>
+        <v>0.04439321814931664</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5234303093951337</v>
+        <v>0.8049067835672826</v>
       </c>
       <c r="K21" t="n">
-        <v>12.07855280931184</v>
+        <v>33.54875865887263</v>
       </c>
       <c r="L21" t="n">
-        <v>5.085656401310695</v>
+        <v>7.013289432621546</v>
       </c>
       <c r="M21" t="n">
-        <v>2.488565991481357</v>
+        <v>4.661878784765735</v>
       </c>
       <c r="N21" t="n">
-        <v>1287.875170447003</v>
+        <v>699.1351771111599</v>
       </c>
       <c r="O21" t="n">
-        <v>1761.730431013427</v>
+        <v>812.777404282489</v>
       </c>
       <c r="P21" t="n">
-        <v>225.8216314644981</v>
+        <v>931.7692403199843</v>
       </c>
       <c r="Q21" t="n">
-        <v>78.86238861083984</v>
+        <v>87.18951416015625</v>
       </c>
       <c r="R21" t="n">
-        <v>122.7546005249023</v>
+        <v>56.04081726074219</v>
       </c>
       <c r="S21" t="n">
-        <v>4.614678899082569</v>
+        <v>5.245967741935484</v>
       </c>
       <c r="T21" t="n">
-        <v>5.414871215820312</v>
+        <v>12.03038787841797</v>
       </c>
       <c r="U21" t="n">
-        <v>10.344970703125</v>
+        <v>14.94631195068359</v>
       </c>
       <c r="V21" t="n">
-        <v>10.02840042114258</v>
+        <v>14.77652740478516</v>
       </c>
       <c r="W21" t="n">
         <v>31</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9662948131241368</v>
+        <v>1.423804513940993</v>
       </c>
       <c r="Y21" t="n">
         <v>1</v>
@@ -2426,13 +2484,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC21" t="b">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2447,70 +2508,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>6.209269240294088</v>
+        <v>22.7130017499178</v>
       </c>
       <c r="H22" t="n">
-        <v>2.811740944797386</v>
+        <v>5.377647441738282</v>
       </c>
       <c r="I22" t="n">
-        <v>0.004484639321386891</v>
+        <v>0.02851838036137732</v>
       </c>
       <c r="J22" t="n">
-        <v>1.51765067970525</v>
+        <v>1.258838206046416</v>
       </c>
       <c r="K22" t="n">
-        <v>5.465632435055457</v>
+        <v>13.0555430734509</v>
       </c>
       <c r="L22" t="n">
-        <v>3.51149577424724</v>
+        <v>8.638549078242617</v>
       </c>
       <c r="M22" t="n">
-        <v>2.485918155011591</v>
+        <v>5.225477306731772</v>
       </c>
       <c r="N22" t="n">
-        <v>1384.563795505822</v>
+        <v>796.4337897911694</v>
       </c>
       <c r="O22" t="n">
-        <v>2562.659653797953</v>
+        <v>909.2498489960402</v>
       </c>
       <c r="P22" t="n">
-        <v>225.8216314644981</v>
+        <v>1795.901841890004</v>
       </c>
       <c r="Q22" t="n">
-        <v>40</v>
+        <v>93.84137725830078</v>
       </c>
       <c r="R22" t="n">
-        <v>120.372184753418</v>
+        <v>55.63848495483398</v>
       </c>
       <c r="S22" t="n">
-        <v>5.276595744680851</v>
+        <v>5.310344827586207</v>
       </c>
       <c r="T22" t="n">
-        <v>14.91666793823242</v>
+        <v>20.87104034423828</v>
       </c>
       <c r="U22" t="n">
-        <v>9.828788757324219</v>
+        <v>16.57960510253906</v>
       </c>
       <c r="V22" t="n">
-        <v>10.03609085083008</v>
+        <v>16.69301223754883</v>
       </c>
       <c r="W22" t="n">
         <v>31</v>
       </c>
       <c r="X22" t="n">
-        <v>0.9670358308344049</v>
+        <v>1.608468994372621</v>
       </c>
       <c r="Y22" t="n">
         <v>1</v>
@@ -2519,12 +2580,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC22" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2540,70 +2604,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
-        <v>3.211837614496378</v>
+        <v>9.04624749991461</v>
       </c>
       <c r="H23" t="n">
-        <v>2.022236054975937</v>
+        <v>3.393823809267782</v>
       </c>
       <c r="I23" t="n">
-        <v>0.004682817567266461</v>
+        <v>0.009988818939087395</v>
       </c>
       <c r="J23" t="n">
-        <v>1.577710712978285</v>
+        <v>0.8864143166220915</v>
       </c>
       <c r="K23" t="n">
-        <v>1.623805801764517</v>
+        <v>9.185942438634527</v>
       </c>
       <c r="L23" t="n">
-        <v>1.316136579489406</v>
+        <v>6.060143205454544</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9657916120997774</v>
+        <v>1.668207931911001</v>
       </c>
       <c r="N23" t="n">
-        <v>685.8771601412715</v>
+        <v>905.6373486274343</v>
       </c>
       <c r="O23" t="n">
-        <v>869.0758825923491</v>
+        <v>1058.293695058172</v>
       </c>
       <c r="P23" t="n">
-        <v>487.4232017572836</v>
+        <v>84.70272799371983</v>
       </c>
       <c r="Q23" t="n">
-        <v>39.64285659790039</v>
+        <v>115.1449279785156</v>
       </c>
       <c r="R23" t="n">
-        <v>309.8302612304688</v>
+        <v>65.54805755615234</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>6.043478260869565</v>
       </c>
       <c r="T23" t="n">
-        <v>24.13445281982422</v>
+        <v>13.44717407226562</v>
       </c>
       <c r="U23" t="n">
-        <v>15.29713439941406</v>
+        <v>15.17030334472656</v>
       </c>
       <c r="V23" t="n">
-        <v>15.38671112060547</v>
+        <v>15.02162551879883</v>
       </c>
       <c r="W23" t="n">
         <v>31</v>
       </c>
       <c r="X23" t="n">
-        <v>1.482599270321772</v>
+        <v>1.447421145341012</v>
       </c>
       <c r="Y23" t="n">
         <v>1</v>
@@ -2612,91 +2676,94 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC23" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5_stack1-4</t>
+          <t>4_stack5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>159.7731084543052</v>
+        <v>3.317906255770878</v>
       </c>
       <c r="H24" t="n">
-        <v>14.26286927196913</v>
+        <v>2.055356283122627</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1486856815382389</v>
+        <v>0.004837464269968519</v>
       </c>
       <c r="J24" t="n">
-        <v>1.254862456825359</v>
+        <v>1.61666869813838</v>
       </c>
       <c r="K24" t="n">
-        <v>156.5562928426353</v>
+        <v>1.623805801764517</v>
       </c>
       <c r="L24" t="n">
-        <v>13.41504698676513</v>
+        <v>1.316136579489406</v>
       </c>
       <c r="M24" t="n">
-        <v>11.61503410593651</v>
+        <v>0.9657916120997776</v>
       </c>
       <c r="N24" t="n">
-        <v>1074.569567165853</v>
+        <v>685.8771601412716</v>
       </c>
       <c r="O24" t="n">
-        <v>1640.502348799164</v>
+        <v>869.0758825923491</v>
       </c>
       <c r="P24" t="n">
-        <v>1770.440021386102</v>
+        <v>84.70272799371983</v>
       </c>
       <c r="Q24" t="n">
-        <v>66.03244781494141</v>
+        <v>39.64285659790039</v>
       </c>
       <c r="R24" t="n">
-        <v>414.2842407226562</v>
+        <v>309.8302612304688</v>
       </c>
       <c r="S24" t="n">
-        <v>7.533112582781457</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>27.83477401733398</v>
+        <v>24.13445281982422</v>
       </c>
       <c r="U24" t="n">
-        <v>22.18153381347656</v>
+        <v>14.92850875854492</v>
       </c>
       <c r="V24" t="n">
-        <v>23.04410171508789</v>
+        <v>15.16334533691406</v>
       </c>
       <c r="W24" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="X24" t="n">
-        <v>2.220433471468567</v>
+        <v>1.461076675576216</v>
       </c>
       <c r="Y24" t="n">
         <v>1</v>
@@ -2705,13 +2772,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA24" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AB24" t="n">
         <v>4</v>
       </c>
-      <c r="AC24" t="b">
-        <v>1</v>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2726,70 +2796,70 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>52.92300604165553</v>
+        <v>159.7731084543052</v>
       </c>
       <c r="H25" t="n">
-        <v>8.208755333087579</v>
+        <v>14.26286927196913</v>
       </c>
       <c r="I25" t="n">
-        <v>0.07605058393813122</v>
+        <v>0.1486856815382389</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8785984545048102</v>
+        <v>1.254862456825359</v>
       </c>
       <c r="K25" t="n">
-        <v>55.66872754124617</v>
+        <v>156.5562928426353</v>
       </c>
       <c r="L25" t="n">
-        <v>9.082688817963643</v>
+        <v>13.41504698676513</v>
       </c>
       <c r="M25" t="n">
-        <v>6.721146223425308</v>
+        <v>11.61503410593651</v>
       </c>
       <c r="N25" t="n">
-        <v>695.8921720405136</v>
+        <v>1074.569567165853</v>
       </c>
       <c r="O25" t="n">
-        <v>702.5736233958012</v>
+        <v>1640.502348799164</v>
       </c>
       <c r="P25" t="n">
         <v>1770.440021386102</v>
       </c>
       <c r="Q25" t="n">
-        <v>78.78139495849609</v>
+        <v>66.03244781494141</v>
       </c>
       <c r="R25" t="n">
-        <v>76.29243469238281</v>
+        <v>414.2842407226562</v>
       </c>
       <c r="S25" t="n">
-        <v>8.586046511627908</v>
+        <v>7.533112582781457</v>
       </c>
       <c r="T25" t="n">
-        <v>20.37545776367188</v>
+        <v>27.83477401733398</v>
       </c>
       <c r="U25" t="n">
-        <v>23.19086456298828</v>
+        <v>22.18153381347656</v>
       </c>
       <c r="V25" t="n">
-        <v>23.04589462280273</v>
+        <v>23.04410171508789</v>
       </c>
       <c r="W25" t="n">
         <v>34</v>
       </c>
       <c r="X25" t="n">
-        <v>2.220606228573639</v>
+        <v>2.220433471468567</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
@@ -2803,8 +2873,11 @@
       <c r="AB25" t="n">
         <v>4</v>
       </c>
-      <c r="AC25" t="b">
-        <v>0</v>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2819,70 +2892,70 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8332227718607687</v>
+        <v>52.92300604165553</v>
       </c>
       <c r="H26" t="n">
-        <v>1.02999620519057</v>
+        <v>8.208755333087579</v>
       </c>
       <c r="I26" t="n">
-        <v>0.00162528326920396</v>
+        <v>0.07605058393813122</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0337632389958816</v>
+        <v>0.8785984545048102</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7922867063492064</v>
+        <v>55.66872754124617</v>
       </c>
       <c r="L26" t="n">
-        <v>2.212370925376544</v>
+        <v>9.082688817963643</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4258847412040118</v>
+        <v>6.721146223425308</v>
       </c>
       <c r="N26" t="n">
-        <v>512.6631078094275</v>
+        <v>695.8921720405136</v>
       </c>
       <c r="O26" t="n">
-        <v>438.2257858683884</v>
+        <v>702.5736233958012</v>
       </c>
       <c r="P26" t="n">
-        <v>1109.413498011306</v>
+        <v>1770.440021386102</v>
       </c>
       <c r="Q26" t="n">
-        <v>41.33333206176758</v>
+        <v>78.78139495849609</v>
       </c>
       <c r="R26" t="n">
-        <v>68.57669067382812</v>
+        <v>76.29243469238281</v>
       </c>
       <c r="S26" t="n">
-        <v>7.666666666666667</v>
+        <v>8.586046511627908</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5</v>
+        <v>20.37545776367188</v>
       </c>
       <c r="U26" t="n">
-        <v>14.80900573730469</v>
+        <v>23.19086456298828</v>
       </c>
       <c r="V26" t="n">
-        <v>14.74414825439453</v>
+        <v>23.04589462280273</v>
       </c>
       <c r="W26" t="n">
         <v>34</v>
       </c>
       <c r="X26" t="n">
-        <v>1.420684594137047</v>
+        <v>2.220606228573639</v>
       </c>
       <c r="Y26" t="n">
         <v>1</v>
@@ -2896,14 +2969,17 @@
       <c r="AB26" t="n">
         <v>4</v>
       </c>
-      <c r="AC26" t="b">
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5_stack2-4</t>
+          <t>5_stack1-4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2912,70 +2988,70 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>151.0666420135245</v>
+        <v>0.8332227718607687</v>
       </c>
       <c r="H27" t="n">
-        <v>13.86881474755394</v>
+        <v>1.02999620519057</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1792542256298835</v>
+        <v>0.00162528326920396</v>
       </c>
       <c r="J27" t="n">
-        <v>1.367486288159192</v>
+        <v>-0.0337632389958816</v>
       </c>
       <c r="K27" t="n">
-        <v>144.1192509311667</v>
+        <v>0.7922867063492064</v>
       </c>
       <c r="L27" t="n">
-        <v>14.31150463195192</v>
+        <v>2.212370925376544</v>
       </c>
       <c r="M27" t="n">
-        <v>10.26514340126227</v>
+        <v>0.4258847412040118</v>
       </c>
       <c r="N27" t="n">
-        <v>842.7507997799755</v>
+        <v>512.6631078094275</v>
       </c>
       <c r="O27" t="n">
-        <v>928.9445083072247</v>
+        <v>438.2257858683884</v>
       </c>
       <c r="P27" t="n">
-        <v>1071.475777784383</v>
+        <v>1109.413498011306</v>
       </c>
       <c r="Q27" t="n">
-        <v>67.63302612304688</v>
+        <v>41.33333206176758</v>
       </c>
       <c r="R27" t="n">
-        <v>380.4069519042969</v>
+        <v>68.57669067382812</v>
       </c>
       <c r="S27" t="n">
-        <v>5.771661569826708</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="T27" t="n">
-        <v>25.05013656616211</v>
+        <v>-0.5</v>
       </c>
       <c r="U27" t="n">
-        <v>18.31838226318359</v>
+        <v>14.80900573730469</v>
       </c>
       <c r="V27" t="n">
-        <v>19.6718635559082</v>
+        <v>14.74414825439453</v>
       </c>
       <c r="W27" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="X27" t="n">
-        <v>1.895498675789222</v>
+        <v>1.420684594137047</v>
       </c>
       <c r="Y27" t="n">
         <v>1</v>
@@ -2984,13 +3060,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC27" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3005,70 +3084,70 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>114.304268165868</v>
+        <v>151.0666420135245</v>
       </c>
       <c r="H28" t="n">
-        <v>12.06385984504113</v>
+        <v>13.86881474755394</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09537344755578273</v>
+        <v>0.1792542256298835</v>
       </c>
       <c r="J28" t="n">
-        <v>1.262325283456564</v>
+        <v>1.367486288159192</v>
       </c>
       <c r="K28" t="n">
-        <v>103.3907992765927</v>
+        <v>144.1192509311667</v>
       </c>
       <c r="L28" t="n">
-        <v>13.20714605084964</v>
+        <v>14.31150463195192</v>
       </c>
       <c r="M28" t="n">
-        <v>11.83505557999665</v>
+        <v>10.26514340126227</v>
       </c>
       <c r="N28" t="n">
-        <v>1198.491520388973</v>
+        <v>842.7507997799755</v>
       </c>
       <c r="O28" t="n">
-        <v>1435.316953983437</v>
+        <v>928.9445083072247</v>
       </c>
       <c r="P28" t="n">
         <v>1071.475777784383</v>
       </c>
       <c r="Q28" t="n">
-        <v>67.09868621826172</v>
+        <v>67.63302612304688</v>
       </c>
       <c r="R28" t="n">
-        <v>223.3865051269531</v>
+        <v>380.4069519042969</v>
       </c>
       <c r="S28" t="n">
-        <v>6.421052631578948</v>
+        <v>5.771661569826708</v>
       </c>
       <c r="T28" t="n">
-        <v>23.83005905151367</v>
+        <v>25.05013656616211</v>
       </c>
       <c r="U28" t="n">
-        <v>18.87790679931641</v>
+        <v>18.31838226318359</v>
       </c>
       <c r="V28" t="n">
-        <v>19.6746711730957</v>
+        <v>19.6718635559082</v>
       </c>
       <c r="W28" t="n">
         <v>31</v>
       </c>
       <c r="X28" t="n">
-        <v>1.895769206064399</v>
+        <v>1.895498675789222</v>
       </c>
       <c r="Y28" t="n">
         <v>1</v>
@@ -3077,19 +3156,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC28" t="b">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5_stack3-3</t>
+          <t>5_stack2-4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3098,70 +3180,70 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>120.8965532383836</v>
+        <v>114.304268165868</v>
       </c>
       <c r="H29" t="n">
-        <v>12.40686392305847</v>
+        <v>12.06385984504113</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1195343935408809</v>
+        <v>0.09537344755578273</v>
       </c>
       <c r="J29" t="n">
-        <v>1.640108850990661</v>
+        <v>1.262325283456564</v>
       </c>
       <c r="K29" t="n">
-        <v>114.7747932668596</v>
+        <v>103.3907992765927</v>
       </c>
       <c r="L29" t="n">
-        <v>12.79405631209622</v>
+        <v>13.20714605084964</v>
       </c>
       <c r="M29" t="n">
-        <v>10.90118030482461</v>
+        <v>11.83505557999665</v>
       </c>
       <c r="N29" t="n">
-        <v>1011.395546144941</v>
+        <v>1198.491520388973</v>
       </c>
       <c r="O29" t="n">
-        <v>1434.139982311454</v>
+        <v>1435.316953983437</v>
       </c>
       <c r="P29" t="n">
-        <v>774.2119658305082</v>
+        <v>1071.475777784383</v>
       </c>
       <c r="Q29" t="n">
-        <v>76.7041015625</v>
+        <v>67.09868621826172</v>
       </c>
       <c r="R29" t="n">
-        <v>259.0347595214844</v>
+        <v>223.3865051269531</v>
       </c>
       <c r="S29" t="n">
-        <v>7.105831533477322</v>
+        <v>6.421052631578948</v>
       </c>
       <c r="T29" t="n">
-        <v>23.20724868774414</v>
+        <v>23.83005905151367</v>
       </c>
       <c r="U29" t="n">
-        <v>14.14982223510742</v>
+        <v>18.87790679931641</v>
       </c>
       <c r="V29" t="n">
-        <v>16.14983749389648</v>
+        <v>19.6746711730957</v>
       </c>
       <c r="W29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X29" t="n">
-        <v>1.556130942901847</v>
+        <v>1.895769206064399</v>
       </c>
       <c r="Y29" t="n">
         <v>1</v>
@@ -3170,19 +3252,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA29" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AB29" t="n">
         <v>4</v>
       </c>
-      <c r="AC29" t="b">
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5_stack3-3</t>
+          <t>5_stack2-4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3191,70 +3276,70 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G30" t="n">
-        <v>115.9528084819347</v>
+        <v>10.08828621070902</v>
       </c>
       <c r="H30" t="n">
-        <v>12.15054324227119</v>
+        <v>3.583964975007592</v>
       </c>
       <c r="I30" t="n">
-        <v>0.146072823252851</v>
+        <v>0.01194866024465845</v>
       </c>
       <c r="J30" t="n">
-        <v>2.244003160489637</v>
+        <v>0.6976243137799651</v>
       </c>
       <c r="K30" t="n">
-        <v>126.6905215295324</v>
+        <v>10.37628222941511</v>
       </c>
       <c r="L30" t="n">
-        <v>12.89732920183073</v>
+        <v>3.429052165685547</v>
       </c>
       <c r="M30" t="n">
-        <v>10.33806260506218</v>
+        <v>2.296686171129691</v>
       </c>
       <c r="N30" t="n">
-        <v>793.8013786535862</v>
+        <v>844.3027087676128</v>
       </c>
       <c r="O30" t="n">
-        <v>1045.582401000754</v>
+        <v>994.1487389350906</v>
       </c>
       <c r="P30" t="n">
-        <v>1360.226161310913</v>
+        <v>1080.656156825851</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.68783569335938</v>
+        <v>82.51764678955078</v>
       </c>
       <c r="R30" t="n">
-        <v>104.3067474365234</v>
+        <v>62.62973785400391</v>
       </c>
       <c r="S30" t="n">
-        <v>7.777280858676208</v>
+        <v>5.694117647058824</v>
       </c>
       <c r="T30" t="n">
-        <v>37.92986297607422</v>
+        <v>9.6171875</v>
       </c>
       <c r="U30" t="n">
-        <v>16.90276718139648</v>
+        <v>13.78562545776367</v>
       </c>
       <c r="V30" t="n">
-        <v>19.16870498657227</v>
+        <v>13.7069091796875</v>
       </c>
       <c r="W30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X30" t="n">
-        <v>1.847016415876341</v>
+        <v>1.320740565601249</v>
       </c>
       <c r="Y30" t="n">
         <v>1</v>
@@ -3263,13 +3348,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA30" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AB30" t="n">
         <v>4</v>
       </c>
-      <c r="AC30" t="b">
-        <v>0</v>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -3284,70 +3372,70 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
-        <v>10.04562914723763</v>
+        <v>120.8965532383836</v>
       </c>
       <c r="H31" t="n">
-        <v>3.576379773179454</v>
+        <v>12.40686392305847</v>
       </c>
       <c r="I31" t="n">
-        <v>0.01143364630116524</v>
+        <v>0.1195343935408809</v>
       </c>
       <c r="J31" t="n">
-        <v>1.11000632542288</v>
+        <v>1.640108850990661</v>
       </c>
       <c r="K31" t="n">
-        <v>9.50362101367692</v>
+        <v>114.7747932668596</v>
       </c>
       <c r="L31" t="n">
-        <v>5.508113858416485</v>
+        <v>12.79405631209622</v>
       </c>
       <c r="M31" t="n">
-        <v>3.371930649812463</v>
+        <v>10.90118030482461</v>
       </c>
       <c r="N31" t="n">
-        <v>878.6024057971645</v>
+        <v>1011.395546144941</v>
       </c>
       <c r="O31" t="n">
-        <v>1086.384085629503</v>
+        <v>1434.139982311454</v>
       </c>
       <c r="P31" t="n">
-        <v>1349.084162816139</v>
+        <v>774.2119658305082</v>
       </c>
       <c r="Q31" t="n">
-        <v>59.46575164794922</v>
+        <v>76.7041015625</v>
       </c>
       <c r="R31" t="n">
-        <v>391.5869140625</v>
+        <v>259.0347595214844</v>
       </c>
       <c r="S31" t="n">
-        <v>4.205479452054795</v>
+        <v>7.105831533477322</v>
       </c>
       <c r="T31" t="n">
-        <v>20.93263244628906</v>
+        <v>23.20724868774414</v>
       </c>
       <c r="U31" t="n">
-        <v>18.85811996459961</v>
+        <v>14.14982223510742</v>
       </c>
       <c r="V31" t="n">
-        <v>18.89672470092773</v>
+        <v>16.14983749389648</v>
       </c>
       <c r="W31" t="n">
         <v>30</v>
       </c>
       <c r="X31" t="n">
-        <v>1.820809530605162</v>
+        <v>1.556130942901847</v>
       </c>
       <c r="Y31" t="n">
         <v>1</v>
@@ -3356,19 +3444,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC31" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5_stack3-6</t>
+          <t>5_stack3-3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3377,70 +3468,70 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G32" t="n">
-        <v>48.64368017085827</v>
+        <v>115.9528084819347</v>
       </c>
       <c r="H32" t="n">
-        <v>7.869882921301082</v>
+        <v>12.15054324227119</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07005180239997462</v>
+        <v>0.146072823252851</v>
       </c>
       <c r="J32" t="n">
-        <v>1.071787170024816</v>
+        <v>2.244003160489637</v>
       </c>
       <c r="K32" t="n">
-        <v>51.72639132206793</v>
+        <v>126.6905215295324</v>
       </c>
       <c r="L32" t="n">
-        <v>8.714704566933648</v>
+        <v>12.89732920183073</v>
       </c>
       <c r="M32" t="n">
-        <v>6.576343087132194</v>
+        <v>10.33806260506218</v>
       </c>
       <c r="N32" t="n">
-        <v>694.3958399973432</v>
+        <v>793.8013786535862</v>
       </c>
       <c r="O32" t="n">
-        <v>871.9398469941748</v>
+        <v>1045.582401000754</v>
       </c>
       <c r="P32" t="n">
-        <v>2062.328996037921</v>
+        <v>1360.226161310913</v>
       </c>
       <c r="Q32" t="n">
-        <v>88.95599365234375</v>
+        <v>50.68783569335938</v>
       </c>
       <c r="R32" t="n">
-        <v>222.9918212890625</v>
+        <v>104.3067474365234</v>
       </c>
       <c r="S32" t="n">
-        <v>5.645476772616137</v>
+        <v>7.777280858676208</v>
       </c>
       <c r="T32" t="n">
-        <v>15.89850616455078</v>
+        <v>37.92986297607422</v>
       </c>
       <c r="U32" t="n">
-        <v>14.83364105224609</v>
+        <v>16.90276718139648</v>
       </c>
       <c r="V32" t="n">
-        <v>14.88473510742188</v>
+        <v>19.16870498657227</v>
       </c>
       <c r="W32" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="X32" t="n">
-        <v>1.434230956584577</v>
+        <v>1.847016415876341</v>
       </c>
       <c r="Y32" t="n">
         <v>1</v>
@@ -3449,19 +3540,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA32" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC32" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5_stack3-6</t>
+          <t>5_stack3-3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3470,70 +3564,70 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" t="b">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>33.42440002615467</v>
+        <v>39.07919241579742</v>
       </c>
       <c r="H33" t="n">
-        <v>6.523593171891326</v>
+        <v>7.05387646334324</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04813450499110501</v>
+        <v>0.06899406664869455</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8858810022994785</v>
+        <v>0.8455885080621447</v>
       </c>
       <c r="K33" t="n">
-        <v>38.24032973282041</v>
+        <v>39.27564969859336</v>
       </c>
       <c r="L33" t="n">
-        <v>7.241457568258847</v>
+        <v>8.070497315251489</v>
       </c>
       <c r="M33" t="n">
-        <v>4.456298871358721</v>
+        <v>6.636814847095689</v>
       </c>
       <c r="N33" t="n">
-        <v>694.3958399973433</v>
+        <v>566.4138137382405</v>
       </c>
       <c r="O33" t="n">
-        <v>871.9398469941748</v>
+        <v>602.8448903897632</v>
       </c>
       <c r="P33" t="n">
-        <v>1686.286546839308</v>
+        <v>859.9347359399468</v>
       </c>
       <c r="Q33" t="n">
-        <v>85.19934844970703</v>
+        <v>75.04255676269531</v>
       </c>
       <c r="R33" t="n">
-        <v>222.9918212890625</v>
+        <v>199.9734191894531</v>
       </c>
       <c r="S33" t="n">
-        <v>3.76797385620915</v>
+        <v>5.518617021276595</v>
       </c>
       <c r="T33" t="n">
-        <v>18.9537353515625</v>
+        <v>14.2603645324707</v>
       </c>
       <c r="U33" t="n">
-        <v>21.39535140991211</v>
+        <v>16.86442565917969</v>
       </c>
       <c r="V33" t="n">
-        <v>21.3109130859375</v>
+        <v>16.65656661987305</v>
       </c>
       <c r="W33" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="X33" t="n">
-        <v>2.05343064826828</v>
+        <v>1.604957246751638</v>
       </c>
       <c r="Y33" t="n">
         <v>1</v>
@@ -3542,19 +3636,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA33" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC33" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5_stack3-6</t>
+          <t>5_stack3-3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3563,7 +3660,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="b">
         <v>1</v>
@@ -3575,58 +3672,58 @@
         <v>20</v>
       </c>
       <c r="G34" t="n">
-        <v>7.801744604228981</v>
+        <v>10.04562914723763</v>
       </c>
       <c r="H34" t="n">
-        <v>3.151743921708825</v>
+        <v>3.576379773179454</v>
       </c>
       <c r="I34" t="n">
-        <v>0.01054574820626301</v>
+        <v>0.01143364630116524</v>
       </c>
       <c r="J34" t="n">
-        <v>1.274980402580318</v>
+        <v>1.11000632542288</v>
       </c>
       <c r="K34" t="n">
-        <v>5.383348194409691</v>
+        <v>9.50362101367692</v>
       </c>
       <c r="L34" t="n">
-        <v>8.452171571467112</v>
+        <v>5.508113858416485</v>
       </c>
       <c r="M34" t="n">
-        <v>1.791152272582819</v>
+        <v>3.371930649812463</v>
       </c>
       <c r="N34" t="n">
-        <v>739.8000077031622</v>
+        <v>878.6024057971645</v>
       </c>
       <c r="O34" t="n">
-        <v>821.9577833239575</v>
+        <v>1086.384085629503</v>
       </c>
       <c r="P34" t="n">
-        <v>569.9681483523676</v>
+        <v>1349.084162816139</v>
       </c>
       <c r="Q34" t="n">
-        <v>59.1929817199707</v>
+        <v>59.46575164794922</v>
       </c>
       <c r="R34" t="n">
-        <v>254.222900390625</v>
+        <v>391.5869140625</v>
       </c>
       <c r="S34" t="n">
-        <v>9.105263157894736</v>
+        <v>4.205479452054795</v>
       </c>
       <c r="T34" t="n">
-        <v>23.421875</v>
+        <v>20.93263244628906</v>
       </c>
       <c r="U34" t="n">
-        <v>18.37038040161133</v>
+        <v>18.85811996459961</v>
       </c>
       <c r="V34" t="n">
-        <v>18.46673965454102</v>
+        <v>18.89672470092773</v>
       </c>
       <c r="W34" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="X34" t="n">
-        <v>1.779377965989088</v>
+        <v>1.820809530605162</v>
       </c>
       <c r="Y34" t="n">
         <v>1</v>
@@ -3635,12 +3732,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA34" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB34" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC34" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3656,70 +3756,70 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D35" t="b">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G35" t="n">
-        <v>3.428392670130564</v>
+        <v>33.42440002615467</v>
       </c>
       <c r="H35" t="n">
-        <v>2.089297758216958</v>
+        <v>6.523593171891326</v>
       </c>
       <c r="I35" t="n">
-        <v>0.004634215510181739</v>
+        <v>0.04813450499110501</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9524430214196645</v>
+        <v>0.8858810022994785</v>
       </c>
       <c r="K35" t="n">
-        <v>1.741502968962831</v>
+        <v>38.24032973282041</v>
       </c>
       <c r="L35" t="n">
-        <v>6.071494920142931</v>
+        <v>7.241457568258847</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5197760763066344</v>
+        <v>4.456298871358721</v>
       </c>
       <c r="N35" t="n">
-        <v>739.8000077031622</v>
+        <v>694.3958399973433</v>
       </c>
       <c r="O35" t="n">
-        <v>821.9577833239575</v>
+        <v>871.9398469941748</v>
       </c>
       <c r="P35" t="n">
-        <v>880.1786486980567</v>
+        <v>1686.286546839308</v>
       </c>
       <c r="Q35" t="n">
-        <v>41.33333206176758</v>
+        <v>85.19934844970703</v>
       </c>
       <c r="R35" t="n">
-        <v>254.222900390625</v>
+        <v>222.9918212890625</v>
       </c>
       <c r="S35" t="n">
-        <v>12.22222222222222</v>
+        <v>3.76797385620915</v>
       </c>
       <c r="T35" t="n">
-        <v>21.48554992675781</v>
+        <v>18.9537353515625</v>
       </c>
       <c r="U35" t="n">
-        <v>22.55835723876953</v>
+        <v>21.39535140991211</v>
       </c>
       <c r="V35" t="n">
-        <v>22.55125045776367</v>
+        <v>21.3109130859375</v>
       </c>
       <c r="W35" t="n">
         <v>34</v>
       </c>
       <c r="X35" t="n">
-        <v>2.172944381125698</v>
+        <v>2.05343064826828</v>
       </c>
       <c r="Y35" t="n">
         <v>1</v>
@@ -3731,16 +3831,19 @@
         <v>12</v>
       </c>
       <c r="AB35" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC35" t="b">
+        <v>7</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5_stack4-3</t>
+          <t>5_stack3-6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3749,70 +3852,70 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="b">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G36" t="n">
-        <v>140.5856133071683</v>
+        <v>11.23013727435955</v>
       </c>
       <c r="H36" t="n">
-        <v>13.37905685328875</v>
+        <v>3.781356221056002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1386166044118559</v>
+        <v>0.01517996371644474</v>
       </c>
       <c r="J36" t="n">
-        <v>1.671534611880007</v>
+        <v>1.124260821453235</v>
       </c>
       <c r="K36" t="n">
-        <v>147.7953055226313</v>
+        <v>7.124851163372521</v>
       </c>
       <c r="L36" t="n">
-        <v>14.04823058580443</v>
+        <v>11.47821800436239</v>
       </c>
       <c r="M36" t="n">
-        <v>11.20028333798269</v>
+        <v>8.255651386664816</v>
       </c>
       <c r="N36" t="n">
-        <v>1014.204711648123</v>
+        <v>739.8000077031622</v>
       </c>
       <c r="O36" t="n">
-        <v>1425.038068048117</v>
+        <v>821.9577833239575</v>
       </c>
       <c r="P36" t="n">
-        <v>1384.62870731003</v>
+        <v>1450.146797050424</v>
       </c>
       <c r="Q36" t="n">
-        <v>55.66845703125</v>
+        <v>54.90666580200195</v>
       </c>
       <c r="R36" t="n">
-        <v>204</v>
+        <v>254.222900390625</v>
       </c>
       <c r="S36" t="n">
-        <v>5.24031007751938</v>
+        <v>9.853333333333333</v>
       </c>
       <c r="T36" t="n">
-        <v>38.52297973632812</v>
+        <v>22.74239349365234</v>
       </c>
       <c r="U36" t="n">
-        <v>23.04647445678711</v>
+        <v>20.22875213623047</v>
       </c>
       <c r="V36" t="n">
-        <v>25.53145217895508</v>
+        <v>20.26471328735352</v>
       </c>
       <c r="W36" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="X36" t="n">
-        <v>2.460104181723566</v>
+        <v>1.952623201775428</v>
       </c>
       <c r="Y36" t="n">
         <v>1</v>
@@ -3821,13 +3924,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB36" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC36" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3842,70 +3948,70 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="D37" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>8</v>
-      </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37" t="n">
-        <v>36.85709764350034</v>
+        <v>140.5856133071683</v>
       </c>
       <c r="H37" t="n">
-        <v>6.850395187423118</v>
+        <v>13.37905685328875</v>
       </c>
       <c r="I37" t="n">
-        <v>0.05245190689750179</v>
+        <v>0.1386166044118559</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2978694339199507</v>
+        <v>1.671534611880007</v>
       </c>
       <c r="K37" t="n">
-        <v>37.82596103440427</v>
+        <v>147.7953055226313</v>
       </c>
       <c r="L37" t="n">
-        <v>6.619061567596047</v>
+        <v>14.04823058580443</v>
       </c>
       <c r="M37" t="n">
-        <v>6.38959142926169</v>
+        <v>11.20028333798269</v>
       </c>
       <c r="N37" t="n">
-        <v>702.6836548673846</v>
+        <v>1014.204711648123</v>
       </c>
       <c r="O37" t="n">
-        <v>1053.154252090512</v>
+        <v>1425.038068048117</v>
       </c>
       <c r="P37" t="n">
-        <v>654.0431581210298</v>
+        <v>1384.62870731003</v>
       </c>
       <c r="Q37" t="n">
-        <v>89.31692504882812</v>
+        <v>55.66845703125</v>
       </c>
       <c r="R37" t="n">
-        <v>51.190185546875</v>
+        <v>204</v>
       </c>
       <c r="S37" t="n">
-        <v>4.809230769230769</v>
+        <v>5.24031007751938</v>
       </c>
       <c r="T37" t="n">
-        <v>3.992622375488281</v>
+        <v>38.52297973632812</v>
       </c>
       <c r="U37" t="n">
-        <v>13.40393447875977</v>
+        <v>23.04647445678711</v>
       </c>
       <c r="V37" t="n">
-        <v>12.60011291503906</v>
+        <v>25.53145217895508</v>
       </c>
       <c r="W37" t="n">
         <v>30</v>
       </c>
       <c r="X37" t="n">
-        <v>1.214094296525257</v>
+        <v>2.460104181723566</v>
       </c>
       <c r="Y37" t="n">
         <v>1</v>
@@ -3917,9 +4023,12 @@
         <v>10</v>
       </c>
       <c r="AB37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC37" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3935,70 +4044,70 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
         <v>3</v>
       </c>
-      <c r="D38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>9</v>
-      </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G38" t="n">
-        <v>18.68632198931467</v>
+        <v>73.78574632430438</v>
       </c>
       <c r="H38" t="n">
-        <v>4.877721199745806</v>
+        <v>9.692622455140896</v>
       </c>
       <c r="I38" t="n">
-        <v>0.03041333840411536</v>
+        <v>0.09726908266409612</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9158557966743307</v>
+        <v>0.6272588872933009</v>
       </c>
       <c r="K38" t="n">
-        <v>16.91455728805284</v>
+        <v>79.13110854422064</v>
       </c>
       <c r="L38" t="n">
-        <v>5.268464010874704</v>
+        <v>9.123645964050924</v>
       </c>
       <c r="M38" t="n">
-        <v>3.705793765497156</v>
+        <v>8.307120338103203</v>
       </c>
       <c r="N38" t="n">
-        <v>614.4120629251979</v>
+        <v>758.573477855365</v>
       </c>
       <c r="O38" t="n">
-        <v>672.3646838149007</v>
+        <v>629.0128938968551</v>
       </c>
       <c r="P38" t="n">
-        <v>654.0431581210298</v>
+        <v>270.036533941998</v>
       </c>
       <c r="Q38" t="n">
-        <v>88.85713958740234</v>
+        <v>97.65932464599609</v>
       </c>
       <c r="R38" t="n">
-        <v>62.24539947509766</v>
+        <v>302.5337524414062</v>
       </c>
       <c r="S38" t="n">
-        <v>3.654761904761905</v>
+        <v>4.66813509544787</v>
       </c>
       <c r="T38" t="n">
-        <v>11.647216796875</v>
+        <v>11.80214309692383</v>
       </c>
       <c r="U38" t="n">
-        <v>12.71730422973633</v>
+        <v>18.81542587280273</v>
       </c>
       <c r="V38" t="n">
-        <v>12.66186141967773</v>
+        <v>16.73264694213867</v>
       </c>
       <c r="W38" t="n">
         <v>30</v>
       </c>
       <c r="X38" t="n">
-        <v>1.220044124737614</v>
+        <v>1.612288029099648</v>
       </c>
       <c r="Y38" t="n">
         <v>1</v>
@@ -4010,10 +4119,13 @@
         <v>10</v>
       </c>
       <c r="AB38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC38" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4028,70 +4140,70 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" t="b">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
         <v>12</v>
       </c>
       <c r="G39" t="n">
-        <v>14.89609249563458</v>
+        <v>36.85709764350034</v>
       </c>
       <c r="H39" t="n">
-        <v>4.355030887086181</v>
+        <v>6.850395187423118</v>
       </c>
       <c r="I39" t="n">
-        <v>0.01871812062203853</v>
+        <v>0.05245190689750179</v>
       </c>
       <c r="J39" t="n">
-        <v>1.518886548052596</v>
+        <v>0.2978694339199507</v>
       </c>
       <c r="K39" t="n">
-        <v>15.08886034718747</v>
+        <v>37.82596103440427</v>
       </c>
       <c r="L39" t="n">
-        <v>5.037250676411789</v>
+        <v>6.619061567596047</v>
       </c>
       <c r="M39" t="n">
-        <v>2.876206370119973</v>
+        <v>6.38959142926169</v>
       </c>
       <c r="N39" t="n">
-        <v>795.8113315124207</v>
+        <v>702.6836548673846</v>
       </c>
       <c r="O39" t="n">
-        <v>773.9373391070454</v>
+        <v>1053.154252090512</v>
       </c>
       <c r="P39" t="n">
-        <v>125.1120887318076</v>
+        <v>654.0431581210298</v>
       </c>
       <c r="Q39" t="n">
-        <v>39.10344696044922</v>
+        <v>89.31692504882812</v>
       </c>
       <c r="R39" t="n">
-        <v>302.5337524414062</v>
+        <v>51.190185546875</v>
       </c>
       <c r="S39" t="n">
-        <v>3.603448275862069</v>
+        <v>4.809230769230769</v>
       </c>
       <c r="T39" t="n">
-        <v>7.337661743164062</v>
+        <v>3.992622375488281</v>
       </c>
       <c r="U39" t="n">
-        <v>4.830947875976562</v>
+        <v>13.40393447875977</v>
       </c>
       <c r="V39" t="n">
-        <v>5.125244140625</v>
+        <v>12.60011291503906</v>
       </c>
       <c r="W39" t="n">
         <v>30</v>
       </c>
       <c r="X39" t="n">
-        <v>0.493847136243145</v>
+        <v>1.214094296525257</v>
       </c>
       <c r="Y39" t="n">
         <v>1</v>
@@ -4103,10 +4215,13 @@
         <v>10</v>
       </c>
       <c r="AB39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC39" t="b">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4121,70 +4236,70 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" t="b">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G40" t="n">
-        <v>7.047120303649375</v>
+        <v>18.68632198931467</v>
       </c>
       <c r="H40" t="n">
-        <v>2.995441911824106</v>
+        <v>4.877721199745806</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01094992585125677</v>
+        <v>0.03041333840411536</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9734378641881845</v>
+        <v>0.9158557966743307</v>
       </c>
       <c r="K40" t="n">
-        <v>6.771759661777581</v>
+        <v>16.91455728805284</v>
       </c>
       <c r="L40" t="n">
-        <v>3.228595295480882</v>
+        <v>5.268464010874704</v>
       </c>
       <c r="M40" t="n">
-        <v>2.079088078074016</v>
+        <v>3.705793765497156</v>
       </c>
       <c r="N40" t="n">
-        <v>643.576988499931</v>
+        <v>614.4120629251979</v>
       </c>
       <c r="O40" t="n">
-        <v>699.3173351033145</v>
+        <v>672.3646838149007</v>
       </c>
       <c r="P40" t="n">
         <v>654.0431581210298</v>
       </c>
       <c r="Q40" t="n">
-        <v>106.3818206787109</v>
+        <v>88.85713958740234</v>
       </c>
       <c r="R40" t="n">
-        <v>131.3415069580078</v>
+        <v>62.24539947509766</v>
       </c>
       <c r="S40" t="n">
-        <v>5.454545454545454</v>
+        <v>3.654761904761905</v>
       </c>
       <c r="T40" t="n">
-        <v>12.33114624023438</v>
+        <v>11.647216796875</v>
       </c>
       <c r="U40" t="n">
-        <v>12.66762542724609</v>
+        <v>12.71730422973633</v>
       </c>
       <c r="V40" t="n">
-        <v>12.6604118347168</v>
+        <v>12.66186141967773</v>
       </c>
       <c r="W40" t="n">
         <v>30</v>
       </c>
       <c r="X40" t="n">
-        <v>1.219904448780321</v>
+        <v>1.220044124737614</v>
       </c>
       <c r="Y40" t="n">
         <v>1</v>
@@ -4196,16 +4311,19 @@
         <v>10</v>
       </c>
       <c r="AB40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC40" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5_stack6-5</t>
+          <t>5_stack4-3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4214,70 +4332,70 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D41" t="b">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G41" t="n">
-        <v>300.5587316465168</v>
+        <v>7.047120303649375</v>
       </c>
       <c r="H41" t="n">
-        <v>19.56229185570517</v>
+        <v>2.995441911824106</v>
       </c>
       <c r="I41" t="n">
-        <v>0.202986337413726</v>
+        <v>0.01094992585125677</v>
       </c>
       <c r="J41" t="n">
-        <v>1.207232766607594</v>
+        <v>0.9734378641881845</v>
       </c>
       <c r="K41" t="n">
-        <v>295.0777653045155</v>
+        <v>6.771759661777581</v>
       </c>
       <c r="L41" t="n">
-        <v>15.04986209128067</v>
+        <v>3.228595295480882</v>
       </c>
       <c r="M41" t="n">
-        <v>14.54843784465263</v>
+        <v>2.079088078074016</v>
       </c>
       <c r="N41" t="n">
-        <v>1480.684540033446</v>
+        <v>643.576988499931</v>
       </c>
       <c r="O41" t="n">
-        <v>1934.588337238684</v>
+        <v>699.3173351033145</v>
       </c>
       <c r="P41" t="n">
-        <v>1202.551189654238</v>
+        <v>654.0431581210298</v>
       </c>
       <c r="Q41" t="n">
-        <v>59.60417556762695</v>
+        <v>106.3818206787109</v>
       </c>
       <c r="R41" t="n">
-        <v>515.678955078125</v>
+        <v>131.3415069580078</v>
       </c>
       <c r="S41" t="n">
-        <v>8.039665970772443</v>
+        <v>5.454545454545454</v>
       </c>
       <c r="T41" t="n">
-        <v>21.48818969726562</v>
+        <v>12.33114624023438</v>
       </c>
       <c r="U41" t="n">
-        <v>17.79954147338867</v>
+        <v>12.66762542724609</v>
       </c>
       <c r="V41" t="n">
-        <v>19.05416488647461</v>
+        <v>12.6604118347168</v>
       </c>
       <c r="W41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="X41" t="n">
-        <v>2.141976510423993</v>
+        <v>1.219904448780321</v>
       </c>
       <c r="Y41" t="n">
         <v>1</v>
@@ -4286,13 +4404,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB41" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC41" t="b">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -4307,70 +4428,70 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="b">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F42" t="n">
         <v>14</v>
       </c>
       <c r="G42" t="n">
-        <v>117.3795221485846</v>
+        <v>300.5587316465168</v>
       </c>
       <c r="H42" t="n">
-        <v>12.22506643506262</v>
+        <v>19.56229185570517</v>
       </c>
       <c r="I42" t="n">
-        <v>0.08276967673117519</v>
+        <v>0.202986337413726</v>
       </c>
       <c r="J42" t="n">
-        <v>1.917362563022253</v>
+        <v>1.207232766607594</v>
       </c>
       <c r="K42" t="n">
-        <v>113.5900168732451</v>
+        <v>295.0777653045155</v>
       </c>
       <c r="L42" t="n">
-        <v>13.58026519635713</v>
+        <v>15.04986209128067</v>
       </c>
       <c r="M42" t="n">
-        <v>10.39597856805803</v>
+        <v>14.54843784465263</v>
       </c>
       <c r="N42" t="n">
-        <v>1418.146437007571</v>
+        <v>1480.684540033446</v>
       </c>
       <c r="O42" t="n">
-        <v>2075.432613986</v>
+        <v>1934.588337238684</v>
       </c>
       <c r="P42" t="n">
-        <v>1402.557909113239</v>
+        <v>1202.551189654238</v>
       </c>
       <c r="Q42" t="n">
-        <v>61.72522354125977</v>
+        <v>59.60417556762695</v>
       </c>
       <c r="R42" t="n">
-        <v>191.0262451171875</v>
+        <v>515.678955078125</v>
       </c>
       <c r="S42" t="n">
-        <v>7.649549549549549</v>
+        <v>8.039665970772443</v>
       </c>
       <c r="T42" t="n">
-        <v>30.44603729248047</v>
+        <v>21.48818969726562</v>
       </c>
       <c r="U42" t="n">
-        <v>15.87912368774414</v>
+        <v>17.79954147338867</v>
       </c>
       <c r="V42" t="n">
-        <v>17.99642944335938</v>
+        <v>19.05416488647461</v>
       </c>
       <c r="W42" t="n">
         <v>29</v>
       </c>
       <c r="X42" t="n">
-        <v>2.023071038213873</v>
+        <v>2.141976510423993</v>
       </c>
       <c r="Y42" t="n">
         <v>1</v>
@@ -4379,13 +4500,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB42" t="n">
         <v>5</v>
       </c>
-      <c r="AC42" t="b">
-        <v>1</v>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4400,70 +4524,70 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="b">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G43" t="n">
-        <v>102.0439951929548</v>
+        <v>117.3795221485846</v>
       </c>
       <c r="H43" t="n">
-        <v>11.39852841302047</v>
+        <v>12.22506643506262</v>
       </c>
       <c r="I43" t="n">
-        <v>0.07195429233810977</v>
+        <v>0.08276967673117519</v>
       </c>
       <c r="J43" t="n">
-        <v>1.564392641640039</v>
+        <v>1.917362563022253</v>
       </c>
       <c r="K43" t="n">
-        <v>95.70834957054564</v>
+        <v>113.5900168732451</v>
       </c>
       <c r="L43" t="n">
-        <v>9.763115035575336</v>
+        <v>13.58026519635713</v>
       </c>
       <c r="M43" t="n">
-        <v>6.175011859760761</v>
+        <v>10.39597856805803</v>
       </c>
       <c r="N43" t="n">
-        <v>1418.178011027541</v>
+        <v>1418.146437007571</v>
       </c>
       <c r="O43" t="n">
-        <v>1759.611882003858</v>
+        <v>2075.432613986</v>
       </c>
       <c r="P43" t="n">
-        <v>131.5069681495826</v>
+        <v>1402.557909113239</v>
       </c>
       <c r="Q43" t="n">
-        <v>57.92919921875</v>
+        <v>61.72522354125977</v>
       </c>
       <c r="R43" t="n">
-        <v>321.5603332519531</v>
+        <v>191.0262451171875</v>
       </c>
       <c r="S43" t="n">
-        <v>15.70488721804511</v>
+        <v>7.649549549549549</v>
       </c>
       <c r="T43" t="n">
-        <v>12.80256271362305</v>
+        <v>30.44603729248047</v>
       </c>
       <c r="U43" t="n">
-        <v>8.183727264404297</v>
+        <v>15.87912368774414</v>
       </c>
       <c r="V43" t="n">
-        <v>10.67392349243164</v>
+        <v>17.99642944335938</v>
       </c>
       <c r="W43" t="n">
         <v>29</v>
       </c>
       <c r="X43" t="n">
-        <v>1.199910546123208</v>
+        <v>2.023071038213873</v>
       </c>
       <c r="Y43" t="n">
         <v>1</v>
@@ -4472,13 +4596,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB43" t="n">
         <v>5</v>
       </c>
-      <c r="AC43" t="b">
-        <v>0</v>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -4493,70 +4620,70 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" t="b">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
         <v>15</v>
       </c>
       <c r="G44" t="n">
-        <v>56.060112152408</v>
+        <v>73.55843496036536</v>
       </c>
       <c r="H44" t="n">
-        <v>8.448547311504749</v>
+        <v>9.677680932969771</v>
       </c>
       <c r="I44" t="n">
-        <v>0.03953055247996839</v>
+        <v>0.05500575441584687</v>
       </c>
       <c r="J44" t="n">
-        <v>1.642024522618467</v>
+        <v>1.279813549935389</v>
       </c>
       <c r="K44" t="n">
-        <v>47.49622605723378</v>
+        <v>75.18026143268904</v>
       </c>
       <c r="L44" t="n">
-        <v>11.97229101443594</v>
+        <v>9.041035562339633</v>
       </c>
       <c r="M44" t="n">
-        <v>8.608815846527046</v>
+        <v>8.421043779527462</v>
       </c>
       <c r="N44" t="n">
-        <v>1418.146437007571</v>
+        <v>1337.286175629173</v>
       </c>
       <c r="O44" t="n">
-        <v>2075.432613986</v>
+        <v>1671.770562884849</v>
       </c>
       <c r="P44" t="n">
-        <v>1202.551189654238</v>
+        <v>219.3482872685908</v>
       </c>
       <c r="Q44" t="n">
-        <v>61.4727897644043</v>
+        <v>46.60421752929688</v>
       </c>
       <c r="R44" t="n">
-        <v>191.0262451171875</v>
+        <v>321.5603332519531</v>
       </c>
       <c r="S44" t="n">
-        <v>8.290816326530612</v>
+        <v>15.80272952853598</v>
       </c>
       <c r="T44" t="n">
-        <v>29.83633422851562</v>
+        <v>7.193405151367188</v>
       </c>
       <c r="U44" t="n">
-        <v>18.17045593261719</v>
+        <v>5.62066650390625</v>
       </c>
       <c r="V44" t="n">
-        <v>19.06801605224609</v>
+        <v>6.158042907714844</v>
       </c>
       <c r="W44" t="n">
         <v>29</v>
       </c>
       <c r="X44" t="n">
-        <v>2.143533591088576</v>
+        <v>0.6922572223499182</v>
       </c>
       <c r="Y44" t="n">
         <v>1</v>
@@ -4565,13 +4692,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB44" t="n">
         <v>5</v>
       </c>
-      <c r="AC44" t="b">
-        <v>1</v>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4586,70 +4716,70 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
         <v>5</v>
       </c>
-      <c r="D45" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" t="n">
-        <v>4</v>
-      </c>
       <c r="F45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G45" t="n">
-        <v>5.955703978984613</v>
+        <v>56.060112152408</v>
       </c>
       <c r="H45" t="n">
-        <v>2.753731617783361</v>
+        <v>8.448547311504749</v>
       </c>
       <c r="I45" t="n">
-        <v>0.004846843177527419</v>
+        <v>0.03953055247996839</v>
       </c>
       <c r="J45" t="n">
-        <v>4.22419997054813</v>
+        <v>1.642024522618467</v>
       </c>
       <c r="K45" t="n">
-        <v>2.012310229912006</v>
+        <v>47.49622605723378</v>
       </c>
       <c r="L45" t="n">
-        <v>6.852833546452087</v>
+        <v>11.97229101443594</v>
       </c>
       <c r="M45" t="n">
-        <v>2.30350401513813</v>
+        <v>8.608815846527046</v>
       </c>
       <c r="N45" t="n">
-        <v>1228.780003982483</v>
+        <v>1418.146437007571</v>
       </c>
       <c r="O45" t="n">
-        <v>1479.374926904672</v>
+        <v>2075.432613986</v>
       </c>
       <c r="P45" t="n">
-        <v>438.5004125918511</v>
+        <v>1202.551189654238</v>
       </c>
       <c r="Q45" t="n">
-        <v>63.86956405639648</v>
+        <v>61.4727897644043</v>
       </c>
       <c r="R45" t="n">
-        <v>124.69970703125</v>
+        <v>191.0262451171875</v>
       </c>
       <c r="S45" t="n">
-        <v>3.717391304347826</v>
+        <v>8.290816326530612</v>
       </c>
       <c r="T45" t="n">
-        <v>33.70329666137695</v>
+        <v>29.83633422851562</v>
       </c>
       <c r="U45" t="n">
-        <v>7.978622436523438</v>
+        <v>18.17045593261719</v>
       </c>
       <c r="V45" t="n">
-        <v>8.329521179199219</v>
+        <v>19.06801605224609</v>
       </c>
       <c r="W45" t="n">
         <v>29</v>
       </c>
       <c r="X45" t="n">
-        <v>0.9363642445221293</v>
+        <v>2.143533591088576</v>
       </c>
       <c r="Y45" t="n">
         <v>1</v>
@@ -4658,28 +4788,31 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB45" t="n">
         <v>5</v>
       </c>
-      <c r="AC45" t="b">
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6_stack1-4</t>
+          <t>5_stack6-5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D46" t="b">
         <v>1</v>
@@ -4688,61 +4821,61 @@
         <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G46" t="n">
-        <v>43.75157473970095</v>
+        <v>5.955703978984613</v>
       </c>
       <c r="H46" t="n">
-        <v>7.463660971870526</v>
+        <v>2.753731617783361</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0440491117441834</v>
+        <v>0.004846843177527419</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8300331403341118</v>
+        <v>4.22419997054813</v>
       </c>
       <c r="K46" t="n">
-        <v>38.62119523594079</v>
+        <v>2.012310229912006</v>
       </c>
       <c r="L46" t="n">
-        <v>11.19603698546136</v>
+        <v>6.852833546452087</v>
       </c>
       <c r="M46" t="n">
-        <v>4.366257892702478</v>
+        <v>2.30350401513813</v>
       </c>
       <c r="N46" t="n">
-        <v>993.245334747942</v>
+        <v>1228.780003982483</v>
       </c>
       <c r="O46" t="n">
-        <v>1346.847916639371</v>
+        <v>1479.374926904672</v>
       </c>
       <c r="P46" t="n">
-        <v>943.1466331491546</v>
+        <v>438.5004125918511</v>
       </c>
       <c r="Q46" t="n">
-        <v>51.75650024414062</v>
+        <v>63.86956405639648</v>
       </c>
       <c r="R46" t="n">
-        <v>542.07568359375</v>
+        <v>124.69970703125</v>
       </c>
       <c r="S46" t="n">
-        <v>6.465721040189125</v>
+        <v>3.717391304347826</v>
       </c>
       <c r="T46" t="n">
-        <v>9.913536071777344</v>
+        <v>33.70329666137695</v>
       </c>
       <c r="U46" t="n">
-        <v>11.94354248046875</v>
+        <v>7.978622436523438</v>
       </c>
       <c r="V46" t="n">
-        <v>11.80646133422852</v>
+        <v>8.329521179199219</v>
       </c>
       <c r="W46" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="X46" t="n">
-        <v>1.137621342339247</v>
+        <v>0.9363642445221293</v>
       </c>
       <c r="Y46" t="n">
         <v>1</v>
@@ -4751,13 +4884,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA46" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AB46" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC46" t="b">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -4772,70 +4908,70 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="b">
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G47" t="n">
-        <v>32.06637248952386</v>
+        <v>43.75157473970095</v>
       </c>
       <c r="H47" t="n">
-        <v>6.38969275551411</v>
+        <v>7.463660971870526</v>
       </c>
       <c r="I47" t="n">
-        <v>0.04078951216179397</v>
+        <v>0.0440491117441834</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2455085418419623</v>
+        <v>0.8300331403341118</v>
       </c>
       <c r="K47" t="n">
-        <v>41.34923712532657</v>
+        <v>38.62119523594079</v>
       </c>
       <c r="L47" t="n">
-        <v>4.996611729395731</v>
+        <v>11.19603698546136</v>
       </c>
       <c r="M47" t="n">
-        <v>3.491957778344765</v>
+        <v>4.366257892702478</v>
       </c>
       <c r="N47" t="n">
-        <v>786.1425839644938</v>
+        <v>993.245334747942</v>
       </c>
       <c r="O47" t="n">
-        <v>1082.068522832231</v>
+        <v>1346.847916639371</v>
       </c>
       <c r="P47" t="n">
-        <v>8.081872147617547</v>
+        <v>943.1466331491546</v>
       </c>
       <c r="Q47" t="n">
-        <v>187.7163391113281</v>
+        <v>51.75650024414062</v>
       </c>
       <c r="R47" t="n">
-        <v>462.6748352050781</v>
+        <v>542.07568359375</v>
       </c>
       <c r="S47" t="n">
-        <v>2.372492836676218</v>
+        <v>6.465721040189125</v>
       </c>
       <c r="T47" t="n">
-        <v>4.713764190673828</v>
+        <v>9.913536071777344</v>
       </c>
       <c r="U47" t="n">
-        <v>19.20000076293945</v>
+        <v>11.94354248046875</v>
       </c>
       <c r="V47" t="n">
-        <v>5.386760711669922</v>
+        <v>11.80646133422852</v>
       </c>
       <c r="W47" t="n">
         <v>31</v>
       </c>
       <c r="X47" t="n">
-        <v>0.519045781643657</v>
+        <v>1.137621342339247</v>
       </c>
       <c r="Y47" t="n">
         <v>1</v>
@@ -4847,10 +4983,13 @@
         <v>17</v>
       </c>
       <c r="AB47" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC47" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4865,70 +5004,70 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="b">
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G48" t="n">
-        <v>26.80086460241832</v>
+        <v>32.06637248952386</v>
       </c>
       <c r="H48" t="n">
-        <v>5.841568337774698</v>
+        <v>6.38969275551411</v>
       </c>
       <c r="I48" t="n">
-        <v>0.03478463780915693</v>
+        <v>0.04078951216179397</v>
       </c>
       <c r="J48" t="n">
-        <v>1.626531337675033</v>
+        <v>0.2455085418419623</v>
       </c>
       <c r="K48" t="n">
-        <v>18.19012881466651</v>
+        <v>41.34923712532657</v>
       </c>
       <c r="L48" t="n">
-        <v>8.7432852449531</v>
+        <v>4.996611729395731</v>
       </c>
       <c r="M48" t="n">
-        <v>4.866158139926085</v>
+        <v>3.491957778344765</v>
       </c>
       <c r="N48" t="n">
-        <v>770.4799098228094</v>
+        <v>786.1425839644938</v>
       </c>
       <c r="O48" t="n">
-        <v>832.6682255390041</v>
+        <v>1082.068522832231</v>
       </c>
       <c r="P48" t="n">
-        <v>943.1466331491546</v>
+        <v>8.081872147617547</v>
       </c>
       <c r="Q48" t="n">
-        <v>56.62136077880859</v>
+        <v>187.7163391113281</v>
       </c>
       <c r="R48" t="n">
-        <v>199.6536865234375</v>
+        <v>462.6748352050781</v>
       </c>
       <c r="S48" t="n">
-        <v>5.135922330097087</v>
+        <v>2.372492836676218</v>
       </c>
       <c r="T48" t="n">
-        <v>18.57258987426758</v>
+        <v>4.713764190673828</v>
       </c>
       <c r="U48" t="n">
-        <v>11.41852569580078</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="V48" t="n">
-        <v>11.75580215454102</v>
+        <v>5.386760711669922</v>
       </c>
       <c r="W48" t="n">
         <v>31</v>
       </c>
       <c r="X48" t="n">
-        <v>1.132740035200179</v>
+        <v>0.519045781643657</v>
       </c>
       <c r="Y48" t="n">
         <v>1</v>
@@ -4940,16 +5079,19 @@
         <v>17</v>
       </c>
       <c r="AB48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC48" t="b">
+        <v>3</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6_stack2-5</t>
+          <t>6_stack1-4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4958,70 +5100,70 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" t="b">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
         <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>79.73320089612007</v>
+        <v>26.80086460241832</v>
       </c>
       <c r="H49" t="n">
-        <v>10.07568679590891</v>
+        <v>5.841568337774698</v>
       </c>
       <c r="I49" t="n">
-        <v>0.06495289328926024</v>
+        <v>0.03478463780915693</v>
       </c>
       <c r="J49" t="n">
-        <v>1.376680880771985</v>
+        <v>1.626531337675033</v>
       </c>
       <c r="K49" t="n">
-        <v>84.86667627289903</v>
+        <v>18.19012881466651</v>
       </c>
       <c r="L49" t="n">
-        <v>12.07847816537126</v>
+        <v>8.7432852449531</v>
       </c>
       <c r="M49" t="n">
-        <v>9.956694886143849</v>
+        <v>4.866158139926085</v>
       </c>
       <c r="N49" t="n">
-        <v>1227.554260609107</v>
+        <v>770.4799098228094</v>
       </c>
       <c r="O49" t="n">
-        <v>1597.699812328044</v>
+        <v>832.6682255390041</v>
       </c>
       <c r="P49" t="n">
-        <v>2547.47671922937</v>
+        <v>943.1466331491546</v>
       </c>
       <c r="Q49" t="n">
-        <v>90.22304534912109</v>
+        <v>56.62136077880859</v>
       </c>
       <c r="R49" t="n">
-        <v>541.353759765625</v>
+        <v>199.6536865234375</v>
       </c>
       <c r="S49" t="n">
-        <v>5.933085501858736</v>
+        <v>5.135922330097087</v>
       </c>
       <c r="T49" t="n">
-        <v>16.78974151611328</v>
+        <v>18.57258987426758</v>
       </c>
       <c r="U49" t="n">
-        <v>12.1958122253418</v>
+        <v>11.41852569580078</v>
       </c>
       <c r="V49" t="n">
-        <v>12.4963264465332</v>
+        <v>11.75580215454102</v>
       </c>
       <c r="W49" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X49" t="n">
-        <v>1.204093865551416</v>
+        <v>1.132740035200179</v>
       </c>
       <c r="Y49" t="n">
         <v>1</v>
@@ -5030,13 +5172,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA49" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AB49" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC49" t="b">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -5051,7 +5196,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="b">
         <v>1</v>
@@ -5060,7 +5205,7 @@
         <v>8</v>
       </c>
       <c r="F50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G50" t="n">
         <v>48.83850341545088</v>
@@ -5123,12 +5268,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA50" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB50" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC50" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5144,7 +5292,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" t="b">
         <v>1</v>
@@ -5153,7 +5301,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G51" t="n">
         <v>48.05812291736702</v>
@@ -5216,12 +5364,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA51" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB51" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC51" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5237,70 +5388,70 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" t="b">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F52" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G52" t="n">
-        <v>45.33082073704103</v>
+        <v>44.4984966713931</v>
       </c>
       <c r="H52" t="n">
-        <v>7.597170101932784</v>
+        <v>7.527100746189312</v>
       </c>
       <c r="I52" t="n">
-        <v>0.06107862254378712</v>
+        <v>0.07330469772430966</v>
       </c>
       <c r="J52" t="n">
-        <v>0.4251567937132701</v>
+        <v>1.736462714911674</v>
       </c>
       <c r="K52" t="n">
-        <v>50.3150630796187</v>
+        <v>45.97467377600907</v>
       </c>
       <c r="L52" t="n">
-        <v>10.099119223902</v>
+        <v>8.421175149934694</v>
       </c>
       <c r="M52" t="n">
-        <v>4.770705278356501</v>
+        <v>5.51178959554902</v>
       </c>
       <c r="N52" t="n">
-        <v>742.1716281264115</v>
+        <v>607.0347201859655</v>
       </c>
       <c r="O52" t="n">
-        <v>977.2395792475995</v>
+        <v>660.2418755934743</v>
       </c>
       <c r="P52" t="n">
-        <v>1853.691150984376</v>
+        <v>1123.340996129773</v>
       </c>
       <c r="Q52" t="n">
-        <v>89.32048034667969</v>
+        <v>50.09485244750977</v>
       </c>
       <c r="R52" t="n">
-        <v>150.9243316650391</v>
+        <v>582.2310791015625</v>
       </c>
       <c r="S52" t="n">
-        <v>7.149397590361446</v>
+        <v>8.493224932249323</v>
       </c>
       <c r="T52" t="n">
-        <v>4.763324737548828</v>
+        <v>23.56521606445312</v>
       </c>
       <c r="U52" t="n">
-        <v>11.20368957519531</v>
+        <v>13.57081604003906</v>
       </c>
       <c r="V52" t="n">
-        <v>10.86740112304688</v>
+        <v>14.20478820800781</v>
       </c>
       <c r="W52" t="n">
         <v>29</v>
       </c>
       <c r="X52" t="n">
-        <v>1.047137419363554</v>
+        <v>1.368714110974937</v>
       </c>
       <c r="Y52" t="n">
         <v>1</v>
@@ -5309,12 +5460,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA52" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB52" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC52" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5330,70 +5484,70 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D53" t="b">
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G53" t="n">
-        <v>44.4984966713931</v>
+        <v>38.91963784131318</v>
       </c>
       <c r="H53" t="n">
-        <v>7.527100746189312</v>
+        <v>7.039461766806536</v>
       </c>
       <c r="I53" t="n">
-        <v>0.07330469772430966</v>
+        <v>0.0461221872368662</v>
       </c>
       <c r="J53" t="n">
-        <v>1.736462714911674</v>
+        <v>2.555762892644613</v>
       </c>
       <c r="K53" t="n">
-        <v>45.97467377600907</v>
+        <v>50.82508413747806</v>
       </c>
       <c r="L53" t="n">
-        <v>8.421175149934694</v>
+        <v>5.001562925169558</v>
       </c>
       <c r="M53" t="n">
-        <v>5.51178959554902</v>
+        <v>3.565290178571429</v>
       </c>
       <c r="N53" t="n">
-        <v>607.0347201859655</v>
+        <v>843.8376445903696</v>
       </c>
       <c r="O53" t="n">
-        <v>660.2418755934743</v>
+        <v>1141.348662711115</v>
       </c>
       <c r="P53" t="n">
-        <v>1123.340996129773</v>
+        <v>8.552660816410803</v>
       </c>
       <c r="Q53" t="n">
-        <v>50.09485244750977</v>
+        <v>181.2201538085938</v>
       </c>
       <c r="R53" t="n">
-        <v>582.2310791015625</v>
+        <v>481.0960998535156</v>
       </c>
       <c r="S53" t="n">
-        <v>8.493224932249323</v>
+        <v>2.787798408488064</v>
       </c>
       <c r="T53" t="n">
-        <v>23.56521606445312</v>
+        <v>9.341758728027344</v>
       </c>
       <c r="U53" t="n">
-        <v>13.57081604003906</v>
+        <v>3.655174255371094</v>
       </c>
       <c r="V53" t="n">
-        <v>14.20478820800781</v>
+        <v>9.166133880615234</v>
       </c>
       <c r="W53" t="n">
         <v>29</v>
       </c>
       <c r="X53" t="n">
-        <v>1.368714110974937</v>
+        <v>0.8832104077701735</v>
       </c>
       <c r="Y53" t="n">
         <v>1</v>
@@ -5402,19 +5556,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA53" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AB53" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC53" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6_stack2-5</t>
+          <t>6_stack3-3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5423,70 +5580,68 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D54" t="b">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F54" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G54" t="n">
-        <v>38.91963784131316</v>
+        <v>17.41430816740908</v>
       </c>
       <c r="H54" t="n">
-        <v>7.039461766806535</v>
+        <v>4.70877752744274</v>
       </c>
       <c r="I54" t="n">
-        <v>0.02572960193284055</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.555762892644613</v>
-      </c>
+        <v>0.00632449356473488</v>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
-        <v>50.82508413747806</v>
+        <v>18.8207945349115</v>
       </c>
       <c r="L54" t="n">
-        <v>5.001562925169559</v>
+        <v>3.020418547205363</v>
       </c>
       <c r="M54" t="n">
-        <v>3.565290178571429</v>
+        <v>3.020418547205362</v>
       </c>
       <c r="N54" t="n">
-        <v>1512.640496456233</v>
+        <v>2753.470770293855</v>
       </c>
       <c r="O54" t="n">
-        <v>1776.521041691349</v>
+        <v>4801.534400633343</v>
       </c>
       <c r="P54" t="n">
-        <v>8.552660816410803</v>
+        <v>13.45670944967388</v>
       </c>
       <c r="Q54" t="n">
-        <v>181.2201538085938</v>
+        <v>88.57360076904297</v>
       </c>
       <c r="R54" t="n">
-        <v>481.0960998535156</v>
+        <v>307.4601135253906</v>
       </c>
       <c r="S54" t="n">
-        <v>2.787798408488064</v>
+        <v>1.241116751269036</v>
       </c>
       <c r="T54" t="n">
-        <v>9.341758728027344</v>
+        <v>4.545112609863281</v>
       </c>
       <c r="U54" t="n">
-        <v>3.655174255371094</v>
+        <v>-6</v>
       </c>
       <c r="V54" t="n">
-        <v>9.166133880615234</v>
+        <v>4.531913757324219</v>
       </c>
       <c r="W54" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X54" t="n">
-        <v>0.8832104077701735</v>
+        <v>0.5094556950300352</v>
       </c>
       <c r="Y54" t="n">
         <v>1</v>
@@ -5495,19 +5650,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA54" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AB54" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC54" t="b">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6_stack3-3</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5522,64 +5680,64 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G55" t="n">
-        <v>62.52932995441</v>
+        <v>186.0262526483334</v>
       </c>
       <c r="H55" t="n">
-        <v>8.922713466415235</v>
+        <v>15.39012609534933</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1299294518158336</v>
+        <v>0.1898014136918895</v>
       </c>
       <c r="J55" t="n">
-        <v>0.949560041319471</v>
+        <v>1.162326119527621</v>
       </c>
       <c r="K55" t="n">
-        <v>70.28887474750144</v>
+        <v>186.7898931332697</v>
       </c>
       <c r="L55" t="n">
-        <v>8.019135769799956</v>
+        <v>15.09771608004952</v>
       </c>
       <c r="M55" t="n">
-        <v>4.774604555819131</v>
+        <v>11.89827889294968</v>
       </c>
       <c r="N55" t="n">
-        <v>481.2560130172886</v>
+        <v>980.1099424386563</v>
       </c>
       <c r="O55" t="n">
-        <v>443.7575527267092</v>
+        <v>1283.879932188273</v>
       </c>
       <c r="P55" t="n">
-        <v>34.32834043284153</v>
+        <v>986.1060991765391</v>
       </c>
       <c r="Q55" t="n">
-        <v>72.22152709960938</v>
+        <v>81.53159332275391</v>
       </c>
       <c r="R55" t="n">
-        <v>457.0224914550781</v>
+        <v>577.5643920898438</v>
       </c>
       <c r="S55" t="n">
-        <v>3.143929912390488</v>
+        <v>5.400512382578992</v>
       </c>
       <c r="T55" t="n">
-        <v>14.84699630737305</v>
+        <v>18.31843948364258</v>
       </c>
       <c r="U55" t="n">
-        <v>15.63565826416016</v>
+        <v>15.76015472412109</v>
       </c>
       <c r="V55" t="n">
-        <v>14.98466491699219</v>
+        <v>16.34563064575195</v>
       </c>
       <c r="W55" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X55" t="n">
-        <v>1.684503123595583</v>
+        <v>1.837496269181553</v>
       </c>
       <c r="Y55" t="n">
         <v>1</v>
@@ -5588,19 +5746,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA55" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AB55" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC55" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6_stack3-3</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5615,64 +5776,64 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G56" t="n">
-        <v>36.61383978079879</v>
+        <v>94.51659405418904</v>
       </c>
       <c r="H56" t="n">
-        <v>6.827751364359312</v>
+        <v>10.97006222331824</v>
       </c>
       <c r="I56" t="n">
-        <v>0.01351803270678132</v>
+        <v>0.07275431784871943</v>
       </c>
       <c r="J56" t="n">
-        <v>0.4345852486992505</v>
+        <v>0.9726178803942819</v>
       </c>
       <c r="K56" t="n">
-        <v>45.75854255078451</v>
+        <v>85.76727728676696</v>
       </c>
       <c r="L56" t="n">
-        <v>4</v>
+        <v>11.41605691482973</v>
       </c>
       <c r="M56" t="n">
-        <v>3.384080996594768</v>
+        <v>10.39615329719646</v>
       </c>
       <c r="N56" t="n">
-        <v>2708.518360251598</v>
+        <v>1299.120063921438</v>
       </c>
       <c r="O56" t="n">
-        <v>4766.539109586379</v>
+        <v>1347.946423533222</v>
       </c>
       <c r="P56" t="n">
-        <v>21.22472248476259</v>
+        <v>763.6192207826599</v>
       </c>
       <c r="Q56" t="n">
-        <v>150.8370819091797</v>
+        <v>61.33242797851562</v>
       </c>
       <c r="R56" t="n">
-        <v>424.1329345703125</v>
+        <v>144.8813934326172</v>
       </c>
       <c r="S56" t="n">
-        <v>2.743445692883895</v>
+        <v>6.454710144927536</v>
       </c>
       <c r="T56" t="n">
-        <v>11.7719612121582</v>
+        <v>15.51880645751953</v>
       </c>
       <c r="U56" t="n">
-        <v>27.08780670166016</v>
+        <v>15.95570755004883</v>
       </c>
       <c r="V56" t="n">
-        <v>14.2345085144043</v>
+        <v>15.88437271118164</v>
       </c>
       <c r="W56" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X56" t="n">
-        <v>1.600174190626812</v>
+        <v>1.78564389638102</v>
       </c>
       <c r="Y56" t="n">
         <v>1</v>
@@ -5681,19 +5842,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA56" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AB56" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC56" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6_stack3-3</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5708,64 +5872,64 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G57" t="n">
-        <v>17.63323786951817</v>
+        <v>55.85598724464249</v>
       </c>
       <c r="H57" t="n">
-        <v>4.738284051974105</v>
+        <v>8.433151947528376</v>
       </c>
       <c r="I57" t="n">
-        <v>0.00651028921505269</v>
+        <v>0.06540975879958627</v>
       </c>
       <c r="J57" t="n">
-        <v>0.6030969680844871</v>
+        <v>3.061150700523096</v>
       </c>
       <c r="K57" t="n">
-        <v>17.42266861465543</v>
+        <v>57.63312869313443</v>
       </c>
       <c r="L57" t="n">
-        <v>4.866182405381386</v>
+        <v>11.15644066652893</v>
       </c>
       <c r="M57" t="n">
-        <v>3.943845936830475</v>
+        <v>6.933821433809595</v>
       </c>
       <c r="N57" t="n">
-        <v>2708.518360251598</v>
+        <v>853.9396608353766</v>
       </c>
       <c r="O57" t="n">
-        <v>4766.539109586379</v>
+        <v>799.281462443749</v>
       </c>
       <c r="P57" t="n">
-        <v>35.38761493762635</v>
+        <v>552.3135732726206</v>
       </c>
       <c r="Q57" t="n">
-        <v>62.76351165771484</v>
+        <v>86.10136413574219</v>
       </c>
       <c r="R57" t="n">
-        <v>424.1329345703125</v>
+        <v>83.98568725585938</v>
       </c>
       <c r="S57" t="n">
-        <v>3.168918918918919</v>
+        <v>6.723196881091618</v>
       </c>
       <c r="T57" t="n">
-        <v>8.102291107177734</v>
+        <v>42.26966094970703</v>
       </c>
       <c r="U57" t="n">
-        <v>13.43447494506836</v>
+        <v>13.80842208862305</v>
       </c>
       <c r="V57" t="n">
-        <v>11.48549270629883</v>
+        <v>18.19149398803711</v>
       </c>
       <c r="W57" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X57" t="n">
-        <v>1.291143208538171</v>
+        <v>2.044999245259716</v>
       </c>
       <c r="Y57" t="n">
         <v>1</v>
@@ -5774,19 +5938,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA57" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AB57" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC57" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6_stack3-3</t>
+          <t>6_stack3-6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5801,62 +5968,64 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F58" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G58" t="n">
-        <v>17.41430816740908</v>
+        <v>49.40773961214284</v>
       </c>
       <c r="H58" t="n">
-        <v>4.70877752744274</v>
+        <v>7.931449293171974</v>
       </c>
       <c r="I58" t="n">
-        <v>0.006429459154853743</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>0.05664831783368499</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9106703556785226</v>
+      </c>
       <c r="K58" t="n">
-        <v>18.8207945349115</v>
+        <v>47.79464152310411</v>
       </c>
       <c r="L58" t="n">
-        <v>3.020418547205363</v>
+        <v>10.06777200409825</v>
       </c>
       <c r="M58" t="n">
-        <v>3.020418547205362</v>
+        <v>6.717816235744091</v>
       </c>
       <c r="N58" t="n">
-        <v>2708.518360251598</v>
+        <v>872.1837029159468</v>
       </c>
       <c r="O58" t="n">
-        <v>4766.539109586379</v>
+        <v>1093.681309995798</v>
       </c>
       <c r="P58" t="n">
-        <v>13.45670944967388</v>
+        <v>763.6192207826599</v>
       </c>
       <c r="Q58" t="n">
-        <v>88.57360076904297</v>
+        <v>52.60358047485352</v>
       </c>
       <c r="R58" t="n">
-        <v>424.1329345703125</v>
+        <v>196.5623779296875</v>
       </c>
       <c r="S58" t="n">
-        <v>1.241116751269036</v>
+        <v>7.432225063938619</v>
       </c>
       <c r="T58" t="n">
-        <v>4.545112609863281</v>
+        <v>14.59002685546875</v>
       </c>
       <c r="U58" t="n">
-        <v>-6</v>
+        <v>16.02119445800781</v>
       </c>
       <c r="V58" t="n">
-        <v>4.531913757324219</v>
+        <v>15.8844108581543</v>
       </c>
       <c r="W58" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X58" t="n">
-        <v>0.5094556950300352</v>
+        <v>1.785648184678086</v>
       </c>
       <c r="Y58" t="n">
         <v>1</v>
@@ -5865,13 +6034,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA58" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AB58" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC58" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5886,70 +6058,70 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D59" t="b">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F59" t="n">
         <v>25</v>
       </c>
       <c r="G59" t="n">
-        <v>186.0262526483334</v>
+        <v>42.26585320059611</v>
       </c>
       <c r="H59" t="n">
-        <v>15.39012609534933</v>
+        <v>7.335840489471551</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1898014136918895</v>
+        <v>0.04446523192118957</v>
       </c>
       <c r="J59" t="n">
-        <v>1.162326119527621</v>
+        <v>2.050625931305275</v>
       </c>
       <c r="K59" t="n">
-        <v>186.7898931332697</v>
+        <v>40.04016240341713</v>
       </c>
       <c r="L59" t="n">
-        <v>15.09771608004952</v>
+        <v>7.320879511477454</v>
       </c>
       <c r="M59" t="n">
-        <v>11.89827889294968</v>
+        <v>6.706809836805268</v>
       </c>
       <c r="N59" t="n">
-        <v>980.1099424386563</v>
+        <v>950.5371134802209</v>
       </c>
       <c r="O59" t="n">
-        <v>1283.879932188273</v>
+        <v>1530.377032690608</v>
       </c>
       <c r="P59" t="n">
-        <v>986.1060991765391</v>
+        <v>1177.481693040997</v>
       </c>
       <c r="Q59" t="n">
-        <v>81.53159332275391</v>
+        <v>93.31436157226562</v>
       </c>
       <c r="R59" t="n">
-        <v>577.5643920898438</v>
+        <v>98.52761077880859</v>
       </c>
       <c r="S59" t="n">
-        <v>5.400512382578992</v>
+        <v>6.552845528455284</v>
       </c>
       <c r="T59" t="n">
-        <v>18.31843948364258</v>
+        <v>13.29224014282227</v>
       </c>
       <c r="U59" t="n">
-        <v>15.76015472412109</v>
+        <v>6.482040405273438</v>
       </c>
       <c r="V59" t="n">
-        <v>16.34563064575195</v>
+        <v>6.942577362060547</v>
       </c>
       <c r="W59" t="n">
         <v>27</v>
       </c>
       <c r="X59" t="n">
-        <v>1.837496269181553</v>
+        <v>0.780450768634366</v>
       </c>
       <c r="Y59" t="n">
         <v>1</v>
@@ -5961,10 +6133,13 @@
         <v>21</v>
       </c>
       <c r="AB59" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC59" t="b">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5979,7 +6154,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D60" t="b">
         <v>1</v>
@@ -5988,28 +6163,28 @@
         <v>21</v>
       </c>
       <c r="F60" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G60" t="n">
-        <v>94.51659405418904</v>
+        <v>35.75997917565314</v>
       </c>
       <c r="H60" t="n">
-        <v>10.97006222331824</v>
+        <v>6.747667715985095</v>
       </c>
       <c r="I60" t="n">
-        <v>0.07275431784871943</v>
+        <v>0.02752630812868091</v>
       </c>
       <c r="J60" t="n">
-        <v>0.9726178803942819</v>
+        <v>1.862897384069325</v>
       </c>
       <c r="K60" t="n">
-        <v>85.76727728676696</v>
+        <v>28.55877211905451</v>
       </c>
       <c r="L60" t="n">
-        <v>11.41605691482973</v>
+        <v>9.465584107012374</v>
       </c>
       <c r="M60" t="n">
-        <v>10.39615329719646</v>
+        <v>9.317305434195426</v>
       </c>
       <c r="N60" t="n">
         <v>1299.120063921438</v>
@@ -6018,31 +6193,31 @@
         <v>1347.946423533222</v>
       </c>
       <c r="P60" t="n">
-        <v>763.6192207826599</v>
+        <v>986.1060991765391</v>
       </c>
       <c r="Q60" t="n">
-        <v>61.33242797851562</v>
+        <v>66.61635589599609</v>
       </c>
       <c r="R60" t="n">
         <v>144.8813934326172</v>
       </c>
       <c r="S60" t="n">
-        <v>6.454710144927536</v>
+        <v>5.062893081761007</v>
       </c>
       <c r="T60" t="n">
-        <v>15.51880645751953</v>
+        <v>29.01906967163086</v>
       </c>
       <c r="U60" t="n">
-        <v>15.95570755004883</v>
+        <v>15.57738494873047</v>
       </c>
       <c r="V60" t="n">
-        <v>15.88437271118164</v>
+        <v>16.34396362304688</v>
       </c>
       <c r="W60" t="n">
         <v>27</v>
       </c>
       <c r="X60" t="n">
-        <v>1.78564389638102</v>
+        <v>1.837308870599778</v>
       </c>
       <c r="Y60" t="n">
         <v>1</v>
@@ -6054,9 +6229,12 @@
         <v>21</v>
       </c>
       <c r="AB60" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC60" t="b">
+        <v>5</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6072,70 +6250,70 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D61" t="b">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F61" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G61" t="n">
-        <v>49.74915836523346</v>
+        <v>12.96274146830324</v>
       </c>
       <c r="H61" t="n">
-        <v>7.958806176048475</v>
+        <v>4.062594619897736</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05846268035222053</v>
+        <v>0.01322580346042613</v>
       </c>
       <c r="J61" t="n">
-        <v>1.867539422265682</v>
+        <v>1.242965202770996</v>
       </c>
       <c r="K61" t="n">
-        <v>56.79779013520556</v>
+        <v>11.04705230605245</v>
       </c>
       <c r="L61" t="n">
-        <v>10.33664806936092</v>
+        <v>9.272378767530702</v>
       </c>
       <c r="M61" t="n">
-        <v>5.413008479759606</v>
+        <v>1.784445470901258</v>
       </c>
       <c r="N61" t="n">
-        <v>850.9558245620855</v>
+        <v>980.1099424386563</v>
       </c>
       <c r="O61" t="n">
-        <v>1266.029195163195</v>
+        <v>1283.879932188273</v>
       </c>
       <c r="P61" t="n">
-        <v>1279.603601780068</v>
+        <v>763.6192207826599</v>
       </c>
       <c r="Q61" t="n">
-        <v>94.17994689941406</v>
+        <v>105.0299987792969</v>
       </c>
       <c r="R61" t="n">
-        <v>62.650146484375</v>
+        <v>577.5643920898438</v>
       </c>
       <c r="S61" t="n">
-        <v>6.249357326478149</v>
+        <v>5.26</v>
       </c>
       <c r="T61" t="n">
-        <v>40.36214447021484</v>
+        <v>19.58560180664062</v>
       </c>
       <c r="U61" t="n">
-        <v>21.61247253417969</v>
+        <v>15.75716018676758</v>
       </c>
       <c r="V61" t="n">
-        <v>22.88908386230469</v>
+        <v>15.88384246826172</v>
       </c>
       <c r="W61" t="n">
         <v>27</v>
       </c>
       <c r="X61" t="n">
-        <v>2.573079443276122</v>
+        <v>1.785584289051806</v>
       </c>
       <c r="Y61" t="n">
         <v>1</v>
@@ -6147,16 +6325,19 @@
         <v>21</v>
       </c>
       <c r="AB61" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC61" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack4-5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6165,70 +6346,70 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D62" t="b">
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F62" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G62" t="n">
-        <v>49.40773961214284</v>
+        <v>69.20216447183583</v>
       </c>
       <c r="H62" t="n">
-        <v>7.931449293171974</v>
+        <v>9.386742373518521</v>
       </c>
       <c r="I62" t="n">
-        <v>0.05664831783368499</v>
+        <v>0.07772773179614412</v>
       </c>
       <c r="J62" t="n">
-        <v>0.9106703556785226</v>
+        <v>0.8263367290272944</v>
       </c>
       <c r="K62" t="n">
-        <v>47.79464152310411</v>
+        <v>68.46786923647588</v>
       </c>
       <c r="L62" t="n">
-        <v>10.06777200409825</v>
+        <v>10.55774251794342</v>
       </c>
       <c r="M62" t="n">
-        <v>6.717816235744091</v>
+        <v>8.108088110730542</v>
       </c>
       <c r="N62" t="n">
-        <v>872.1837029159468</v>
+        <v>890.3149863337293</v>
       </c>
       <c r="O62" t="n">
-        <v>1093.681309995798</v>
+        <v>1337.039819372845</v>
       </c>
       <c r="P62" t="n">
-        <v>763.6192207826599</v>
+        <v>1150.05825308379</v>
       </c>
       <c r="Q62" t="n">
-        <v>52.60358047485352</v>
+        <v>57.98098754882812</v>
       </c>
       <c r="R62" t="n">
-        <v>196.5623779296875</v>
+        <v>261.7873229980469</v>
       </c>
       <c r="S62" t="n">
-        <v>7.432225063938619</v>
+        <v>6.835234474017744</v>
       </c>
       <c r="T62" t="n">
-        <v>14.59002685546875</v>
+        <v>43.94636535644531</v>
       </c>
       <c r="U62" t="n">
-        <v>16.02119445800781</v>
+        <v>53.18215179443359</v>
       </c>
       <c r="V62" t="n">
-        <v>15.8844108581543</v>
+        <v>52.22322082519531</v>
       </c>
       <c r="W62" t="n">
         <v>27</v>
       </c>
       <c r="X62" t="n">
-        <v>1.785648184678086</v>
+        <v>5.870680398365645</v>
       </c>
       <c r="Y62" t="n">
         <v>1</v>
@@ -6237,19 +6418,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA62" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AB62" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC62" t="b">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack4-5</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6258,70 +6442,70 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D63" t="b">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G63" t="n">
-        <v>42.26585320059611</v>
+        <v>63.07908534733534</v>
       </c>
       <c r="H63" t="n">
-        <v>7.335840489471551</v>
+        <v>8.961851700957327</v>
       </c>
       <c r="I63" t="n">
-        <v>0.04446523192118957</v>
+        <v>0.1110238712963609</v>
       </c>
       <c r="J63" t="n">
-        <v>2.050625931305275</v>
+        <v>1.277447688687109</v>
       </c>
       <c r="K63" t="n">
-        <v>40.04016240341713</v>
+        <v>65.88998994565365</v>
       </c>
       <c r="L63" t="n">
-        <v>7.320879511477454</v>
+        <v>9.679764503758232</v>
       </c>
       <c r="M63" t="n">
-        <v>6.706809836805268</v>
+        <v>8.673695681163871</v>
       </c>
       <c r="N63" t="n">
-        <v>950.5371134802209</v>
+        <v>568.1578620056904</v>
       </c>
       <c r="O63" t="n">
-        <v>1530.377032690608</v>
+        <v>692.2162726823495</v>
       </c>
       <c r="P63" t="n">
-        <v>1177.481693040997</v>
+        <v>998.9350904011553</v>
       </c>
       <c r="Q63" t="n">
-        <v>93.31436157226562</v>
+        <v>67.70275115966797</v>
       </c>
       <c r="R63" t="n">
-        <v>98.52761077880859</v>
+        <v>228.5398712158203</v>
       </c>
       <c r="S63" t="n">
-        <v>6.552845528455284</v>
+        <v>7.097247706422018</v>
       </c>
       <c r="T63" t="n">
-        <v>13.29224014282227</v>
+        <v>20.11036682128906</v>
       </c>
       <c r="U63" t="n">
-        <v>6.482040405273438</v>
+        <v>15.74261474609375</v>
       </c>
       <c r="V63" t="n">
-        <v>6.942577362060547</v>
+        <v>16.15397262573242</v>
       </c>
       <c r="W63" t="n">
         <v>27</v>
       </c>
       <c r="X63" t="n">
-        <v>0.780450768634366</v>
+        <v>1.815951007063683</v>
       </c>
       <c r="Y63" t="n">
         <v>1</v>
@@ -6330,19 +6514,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA63" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AB63" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC63" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack4-5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6351,70 +6538,70 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D64" t="b">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G64" t="n">
-        <v>35.75997917565314</v>
+        <v>51.48332232385754</v>
       </c>
       <c r="H64" t="n">
-        <v>6.747667715985095</v>
+        <v>8.096332618975213</v>
       </c>
       <c r="I64" t="n">
-        <v>0.02752630812868091</v>
+        <v>0.07700582286928774</v>
       </c>
       <c r="J64" t="n">
-        <v>1.862897384069325</v>
+        <v>1.381643443919474</v>
       </c>
       <c r="K64" t="n">
-        <v>28.55877211905451</v>
+        <v>46.74022424476337</v>
       </c>
       <c r="L64" t="n">
-        <v>9.465584107012374</v>
+        <v>10.12527966041368</v>
       </c>
       <c r="M64" t="n">
-        <v>9.317305434195426</v>
+        <v>7.260491839090461</v>
       </c>
       <c r="N64" t="n">
-        <v>1299.120063921438</v>
+        <v>668.5640177009349</v>
       </c>
       <c r="O64" t="n">
-        <v>1347.946423533222</v>
+        <v>709.4785238714356</v>
       </c>
       <c r="P64" t="n">
-        <v>986.1060991765391</v>
+        <v>998.9350904011553</v>
       </c>
       <c r="Q64" t="n">
-        <v>66.61635589599609</v>
+        <v>65.58424377441406</v>
       </c>
       <c r="R64" t="n">
-        <v>144.8813934326172</v>
+        <v>208.7505187988281</v>
       </c>
       <c r="S64" t="n">
-        <v>5.062893081761007</v>
+        <v>5.135667396061269</v>
       </c>
       <c r="T64" t="n">
-        <v>29.01906967163086</v>
+        <v>21.55858993530273</v>
       </c>
       <c r="U64" t="n">
-        <v>15.57738494873047</v>
+        <v>15.60358428955078</v>
       </c>
       <c r="V64" t="n">
-        <v>16.34396362304688</v>
+        <v>16.15402221679688</v>
       </c>
       <c r="W64" t="n">
         <v>27</v>
       </c>
       <c r="X64" t="n">
-        <v>1.837308870599778</v>
+        <v>1.815956581849868</v>
       </c>
       <c r="Y64" t="n">
         <v>1</v>
@@ -6423,19 +6610,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA64" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AB64" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC64" t="b">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack4-5</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6444,70 +6634,70 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D65" t="b">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F65" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G65" t="n">
-        <v>28.78715435409891</v>
+        <v>39.1195777863611</v>
       </c>
       <c r="H65" t="n">
-        <v>6.054167432771723</v>
+        <v>7.057520344351704</v>
       </c>
       <c r="I65" t="n">
-        <v>0.04475226372623568</v>
+        <v>0.07108994774088356</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4315330733000094</v>
+        <v>0.9726257463981821</v>
       </c>
       <c r="K65" t="n">
-        <v>31.54512511791826</v>
+        <v>36.79064106863132</v>
       </c>
       <c r="L65" t="n">
-        <v>5.188340642328225</v>
+        <v>8.840774817367098</v>
       </c>
       <c r="M65" t="n">
-        <v>4.832226158924833</v>
+        <v>5.671762440068829</v>
       </c>
       <c r="N65" t="n">
-        <v>643.2558256762027</v>
+        <v>550.2828322359784</v>
       </c>
       <c r="O65" t="n">
-        <v>750.868694336176</v>
+        <v>686.8806677693593</v>
       </c>
       <c r="P65" t="n">
-        <v>5.531766858320749</v>
+        <v>1150.05825308379</v>
       </c>
       <c r="Q65" t="n">
-        <v>92.43537139892578</v>
+        <v>79.11206817626953</v>
       </c>
       <c r="R65" t="n">
-        <v>766.3905639648438</v>
+        <v>131.190185546875</v>
       </c>
       <c r="S65" t="n">
-        <v>2.41156462585034</v>
+        <v>4.830459770114943</v>
       </c>
       <c r="T65" t="n">
-        <v>18.70904541015625</v>
+        <v>50.87718963623047</v>
       </c>
       <c r="U65" t="n">
-        <v>43.35483551025391</v>
+        <v>52.30911254882812</v>
       </c>
       <c r="V65" t="n">
-        <v>19.60895156860352</v>
+        <v>52.22322082519531</v>
       </c>
       <c r="W65" t="n">
         <v>27</v>
       </c>
       <c r="X65" t="n">
-        <v>2.204342929970394</v>
+        <v>5.870680398365645</v>
       </c>
       <c r="Y65" t="n">
         <v>1</v>
@@ -6516,19 +6706,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA65" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AB65" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC65" t="b">
+        <v>6</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack4-5</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6537,70 +6730,70 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D66" t="b">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G66" t="n">
-        <v>12.96274146830324</v>
+        <v>32.69420766223664</v>
       </c>
       <c r="H66" t="n">
-        <v>4.062594619897736</v>
+        <v>6.45194219435846</v>
       </c>
       <c r="I66" t="n">
-        <v>0.01322580346042613</v>
+        <v>0.03297439370156615</v>
       </c>
       <c r="J66" t="n">
-        <v>1.242965202770996</v>
+        <v>0.7584082964201952</v>
       </c>
       <c r="K66" t="n">
-        <v>11.04705230605245</v>
+        <v>40.14934867826209</v>
       </c>
       <c r="L66" t="n">
-        <v>9.272378767530702</v>
+        <v>4.044637686639684</v>
       </c>
       <c r="M66" t="n">
-        <v>1.784445470901258</v>
+        <v>3.532765598396927</v>
       </c>
       <c r="N66" t="n">
-        <v>980.1099424386563</v>
+        <v>991.502920664279</v>
       </c>
       <c r="O66" t="n">
-        <v>1283.879932188273</v>
+        <v>1277.014264101705</v>
       </c>
       <c r="P66" t="n">
-        <v>763.6192207826599</v>
+        <v>12.63282927928568</v>
       </c>
       <c r="Q66" t="n">
-        <v>105.0299987792969</v>
+        <v>110.8883361816406</v>
       </c>
       <c r="R66" t="n">
-        <v>577.5643920898438</v>
+        <v>357.3987731933594</v>
       </c>
       <c r="S66" t="n">
-        <v>5.26</v>
+        <v>2.607940446650124</v>
       </c>
       <c r="T66" t="n">
-        <v>19.58560180664062</v>
+        <v>12.34288787841797</v>
       </c>
       <c r="U66" t="n">
-        <v>15.75716018676758</v>
+        <v>16.27472686767578</v>
       </c>
       <c r="V66" t="n">
-        <v>15.88384246826172</v>
+        <v>12.7014045715332</v>
       </c>
       <c r="W66" t="n">
         <v>27</v>
       </c>
       <c r="X66" t="n">
-        <v>1.785584289051806</v>
+        <v>1.427830104531529</v>
       </c>
       <c r="Y66" t="n">
         <v>1</v>
@@ -6609,19 +6802,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA66" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AB66" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC66" t="b">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stack4-5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6630,70 +6826,70 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D67" t="b">
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F67" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G67" t="n">
-        <v>11.64058960759878</v>
+        <v>17.76611936501783</v>
       </c>
       <c r="H67" t="n">
-        <v>3.849838829409348</v>
+        <v>4.756104049747635</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3929785653582941</v>
+        <v>0.03221758669323236</v>
       </c>
       <c r="J67" t="n">
-        <v>0.5183075521167365</v>
+        <v>0.9455642173546173</v>
       </c>
       <c r="K67" t="n">
-        <v>12.50819935778221</v>
+        <v>16.59496898175367</v>
       </c>
       <c r="L67" t="n">
-        <v>3.105340102557613</v>
+        <v>5.985586378881651</v>
       </c>
       <c r="M67" t="n">
-        <v>3.090476991582744</v>
+        <v>3.426557963852115</v>
       </c>
       <c r="N67" t="n">
-        <v>29.62143646940538</v>
+        <v>551.4416562041808</v>
       </c>
       <c r="O67" t="n">
-        <v>3.805541739412146</v>
+        <v>768.2094103033942</v>
       </c>
       <c r="P67" t="n">
-        <v>5.531766858320749</v>
+        <v>547.1348979158947</v>
       </c>
       <c r="Q67" t="n">
-        <v>117.0909118652344</v>
+        <v>86.65517425537109</v>
       </c>
       <c r="R67" t="n">
-        <v>975.465087890625</v>
+        <v>515.200439453125</v>
       </c>
       <c r="S67" t="n">
-        <v>1.886363636363636</v>
+        <v>5.482758620689655</v>
       </c>
       <c r="T67" t="n">
-        <v>13.61098480224609</v>
+        <v>10.10122680664062</v>
       </c>
       <c r="U67" t="n">
-        <v>26.26044082641602</v>
+        <v>10.6827507019043</v>
       </c>
       <c r="V67" t="n">
-        <v>19.71089935302734</v>
+        <v>10.65617752075195</v>
       </c>
       <c r="W67" t="n">
         <v>27</v>
       </c>
       <c r="X67" t="n">
-        <v>2.215803403878679</v>
+        <v>1.197915630328209</v>
       </c>
       <c r="Y67" t="n">
         <v>1</v>
@@ -6702,19 +6898,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA67" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AB67" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC67" t="b">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6_stack3-6</t>
+          <t>6_stackf1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6723,70 +6922,70 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D68" t="b">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F68" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G68" t="n">
-        <v>3.801923848084095</v>
+        <v>167.1401132153021</v>
       </c>
       <c r="H68" t="n">
-        <v>2.200172672644661</v>
+        <v>14.58798826628383</v>
       </c>
       <c r="I68" t="n">
-        <v>0.005026066275325094</v>
+        <v>0.1992278605220627</v>
       </c>
       <c r="J68" t="n">
-        <v>0.06074157301868771</v>
+        <v>1.043842058003434</v>
       </c>
       <c r="K68" t="n">
-        <v>3.045720464428176</v>
+        <v>176.507353532041</v>
       </c>
       <c r="L68" t="n">
-        <v>2.073222351944327</v>
+        <v>11.62357420611151</v>
       </c>
       <c r="M68" t="n">
-        <v>1.148846939249538</v>
+        <v>7.18897125571193</v>
       </c>
       <c r="N68" t="n">
-        <v>756.4412484469636</v>
+        <v>838.9394574499926</v>
       </c>
       <c r="O68" t="n">
-        <v>994.5410628257516</v>
+        <v>1023.219939233074</v>
       </c>
       <c r="P68" t="n">
-        <v>23.0294123818034</v>
+        <v>168.0715547591921</v>
       </c>
       <c r="Q68" t="n">
-        <v>128.5483856201172</v>
+        <v>111.0864562988281</v>
       </c>
       <c r="R68" t="n">
-        <v>83.66666412353516</v>
+        <v>585.07568359375</v>
       </c>
       <c r="S68" t="n">
-        <v>2.645161290322581</v>
+        <v>5.408006814310051</v>
       </c>
       <c r="T68" t="n">
-        <v>0.6933326721191406</v>
+        <v>10.11078643798828</v>
       </c>
       <c r="U68" t="n">
-        <v>11.41446685791016</v>
+        <v>9.686126708984375</v>
       </c>
       <c r="V68" t="n">
-        <v>10.20075607299805</v>
+        <v>9.986000061035156</v>
       </c>
       <c r="W68" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="X68" t="n">
-        <v>1.14671936697874</v>
+        <v>0.962209291373328</v>
       </c>
       <c r="Y68" t="n">
         <v>1</v>
@@ -6795,19 +6994,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA68" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB68" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC68" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stackf1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6816,70 +7018,70 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="b">
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F69" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G69" t="n">
-        <v>69.20216447183583</v>
+        <v>120.5582618695273</v>
       </c>
       <c r="H69" t="n">
-        <v>9.386742373518521</v>
+        <v>12.38949338983719</v>
       </c>
       <c r="I69" t="n">
-        <v>0.07772773179614412</v>
+        <v>0.1150591367384773</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8263367290272944</v>
+        <v>1.034337687857007</v>
       </c>
       <c r="K69" t="n">
-        <v>68.46786923647588</v>
+        <v>116.4015465638115</v>
       </c>
       <c r="L69" t="n">
-        <v>10.55774251794342</v>
+        <v>13.40390185384491</v>
       </c>
       <c r="M69" t="n">
-        <v>8.108088110730542</v>
+        <v>10.53782197871894</v>
       </c>
       <c r="N69" t="n">
-        <v>890.3149863337293</v>
+        <v>1047.793902222204</v>
       </c>
       <c r="O69" t="n">
-        <v>1337.039819372845</v>
+        <v>1370.62274441343</v>
       </c>
       <c r="P69" t="n">
-        <v>1150.05825308379</v>
+        <v>1125.616474695607</v>
       </c>
       <c r="Q69" t="n">
-        <v>57.98098754882812</v>
+        <v>77.28485107421875</v>
       </c>
       <c r="R69" t="n">
-        <v>261.7873229980469</v>
+        <v>477</v>
       </c>
       <c r="S69" t="n">
-        <v>6.835234474017744</v>
+        <v>6.942667471333736</v>
       </c>
       <c r="T69" t="n">
-        <v>43.94636535644531</v>
+        <v>14.86717987060547</v>
       </c>
       <c r="U69" t="n">
-        <v>53.18215179443359</v>
+        <v>14.37362289428711</v>
       </c>
       <c r="V69" t="n">
-        <v>52.22322082519531</v>
+        <v>14.44396591186523</v>
       </c>
       <c r="W69" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="X69" t="n">
-        <v>5.870680398365645</v>
+        <v>1.391760276359909</v>
       </c>
       <c r="Y69" t="n">
         <v>1</v>
@@ -6888,19 +7090,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AB69" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC69" t="b">
+        <v>7</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stackf1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6909,70 +7114,70 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="b">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F70" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G70" t="n">
-        <v>63.07908534733534</v>
+        <v>114.9422092400107</v>
       </c>
       <c r="H70" t="n">
-        <v>8.961851700957327</v>
+        <v>12.09747767774775</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1110238712963609</v>
+        <v>0.08236606326709535</v>
       </c>
       <c r="J70" t="n">
-        <v>1.277447688687109</v>
+        <v>1.186249715813747</v>
       </c>
       <c r="K70" t="n">
-        <v>65.88998994565365</v>
+        <v>90.41770624039185</v>
       </c>
       <c r="L70" t="n">
-        <v>9.679764503758232</v>
+        <v>13.52283253157171</v>
       </c>
       <c r="M70" t="n">
-        <v>8.673695681163871</v>
+        <v>12.26630963487948</v>
       </c>
       <c r="N70" t="n">
-        <v>568.1578620056904</v>
+        <v>1395.504467261935</v>
       </c>
       <c r="O70" t="n">
-        <v>692.2162726823495</v>
+        <v>1368.30803345853</v>
       </c>
       <c r="P70" t="n">
-        <v>998.9350904011553</v>
+        <v>1125.616474695607</v>
       </c>
       <c r="Q70" t="n">
-        <v>67.70275115966797</v>
+        <v>68.08979797363281</v>
       </c>
       <c r="R70" t="n">
-        <v>228.5398712158203</v>
+        <v>151.3169708251953</v>
       </c>
       <c r="S70" t="n">
-        <v>7.097247706422018</v>
+        <v>6.123265306122449</v>
       </c>
       <c r="T70" t="n">
-        <v>20.11036682128906</v>
+        <v>16.71946716308594</v>
       </c>
       <c r="U70" t="n">
-        <v>15.74261474609375</v>
+        <v>14.09439086914062</v>
       </c>
       <c r="V70" t="n">
-        <v>16.15397262573242</v>
+        <v>14.43611907958984</v>
       </c>
       <c r="W70" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="X70" t="n">
-        <v>1.815951007063683</v>
+        <v>1.391004188348985</v>
       </c>
       <c r="Y70" t="n">
         <v>1</v>
@@ -6981,19 +7186,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA70" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AB70" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC70" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stackf1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7002,70 +7210,70 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D71" t="b">
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F71" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G71" t="n">
-        <v>51.48332232385754</v>
+        <v>59.18577191536914</v>
       </c>
       <c r="H71" t="n">
-        <v>8.096332618975213</v>
+        <v>8.680879292348431</v>
       </c>
       <c r="I71" t="n">
-        <v>0.07700582286928774</v>
+        <v>0.0818044567253553</v>
       </c>
       <c r="J71" t="n">
-        <v>1.381643443919474</v>
+        <v>0.6597759122399036</v>
       </c>
       <c r="K71" t="n">
-        <v>46.74022424476337</v>
+        <v>60.29831524765081</v>
       </c>
       <c r="L71" t="n">
-        <v>10.12527966041368</v>
+        <v>5.657981975489585</v>
       </c>
       <c r="M71" t="n">
-        <v>7.260491839090461</v>
+        <v>4.624410641007072</v>
       </c>
       <c r="N71" t="n">
-        <v>668.5640177009349</v>
+        <v>723.503025196725</v>
       </c>
       <c r="O71" t="n">
-        <v>709.4785238714356</v>
+        <v>666.6759874003154</v>
       </c>
       <c r="P71" t="n">
-        <v>998.9350904011553</v>
+        <v>38.17311456131978</v>
       </c>
       <c r="Q71" t="n">
-        <v>65.58424377441406</v>
+        <v>77.97145843505859</v>
       </c>
       <c r="R71" t="n">
-        <v>208.7505187988281</v>
+        <v>215.570556640625</v>
       </c>
       <c r="S71" t="n">
-        <v>5.135667396061269</v>
+        <v>10.39449541284404</v>
       </c>
       <c r="T71" t="n">
-        <v>21.55858993530273</v>
+        <v>6.614913940429688</v>
       </c>
       <c r="U71" t="n">
-        <v>15.60358428955078</v>
+        <v>10.0260009765625</v>
       </c>
       <c r="V71" t="n">
-        <v>16.15402221679688</v>
+        <v>7.357421875</v>
       </c>
       <c r="W71" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="X71" t="n">
-        <v>1.815956581849868</v>
+        <v>0.708930467194942</v>
       </c>
       <c r="Y71" t="n">
         <v>1</v>
@@ -7074,19 +7282,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA71" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AB71" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC71" t="b">
+        <v>7</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stackf1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7095,70 +7306,70 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D72" t="b">
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F72" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G72" t="n">
-        <v>39.1195777863611</v>
+        <v>52.38768966104699</v>
       </c>
       <c r="H72" t="n">
-        <v>7.057520344351704</v>
+        <v>8.167134022027462</v>
       </c>
       <c r="I72" t="n">
-        <v>0.07108994774088356</v>
+        <v>0.04999808602621283</v>
       </c>
       <c r="J72" t="n">
-        <v>0.9726257463981821</v>
+        <v>1.74111121966838</v>
       </c>
       <c r="K72" t="n">
-        <v>36.79064106863132</v>
+        <v>55.42482231449618</v>
       </c>
       <c r="L72" t="n">
-        <v>8.840774817367098</v>
+        <v>7.580602160149171</v>
       </c>
       <c r="M72" t="n">
-        <v>5.671762440068829</v>
+        <v>6.355574860925138</v>
       </c>
       <c r="N72" t="n">
-        <v>550.2828322359784</v>
+        <v>1047.793902222204</v>
       </c>
       <c r="O72" t="n">
-        <v>686.8806677693593</v>
+        <v>1370.62274441343</v>
       </c>
       <c r="P72" t="n">
-        <v>1150.05825308379</v>
+        <v>416.7264366601631</v>
       </c>
       <c r="Q72" t="n">
-        <v>79.11206817626953</v>
+        <v>74.39968872070312</v>
       </c>
       <c r="R72" t="n">
-        <v>131.190185546875</v>
+        <v>477</v>
       </c>
       <c r="S72" t="n">
-        <v>4.830459770114943</v>
+        <v>4.537037037037037</v>
       </c>
       <c r="T72" t="n">
-        <v>50.87718963623047</v>
+        <v>22.5695686340332</v>
       </c>
       <c r="U72" t="n">
-        <v>52.30911254882812</v>
+        <v>12.96273803710938</v>
       </c>
       <c r="V72" t="n">
-        <v>52.22322082519531</v>
+        <v>14.50303649902344</v>
       </c>
       <c r="W72" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="X72" t="n">
-        <v>5.870680398365645</v>
+        <v>1.397452071619582</v>
       </c>
       <c r="Y72" t="n">
         <v>1</v>
@@ -7167,19 +7378,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA72" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AB72" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC72" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stackf1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7188,70 +7402,70 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D73" t="b">
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G73" t="n">
-        <v>32.69420766223664</v>
+        <v>44.23710646893255</v>
       </c>
       <c r="H73" t="n">
-        <v>6.45194219435846</v>
+        <v>7.504960579570328</v>
       </c>
       <c r="I73" t="n">
-        <v>0.03297439370156615</v>
+        <v>0.04789549974336052</v>
       </c>
       <c r="J73" t="n">
-        <v>0.7584082964201952</v>
+        <v>1.043379232724821</v>
       </c>
       <c r="K73" t="n">
-        <v>40.14934867826209</v>
+        <v>43.80161452731908</v>
       </c>
       <c r="L73" t="n">
-        <v>4.044637686639684</v>
+        <v>8.341678666274161</v>
       </c>
       <c r="M73" t="n">
-        <v>3.532765598396927</v>
+        <v>6.116589750012188</v>
       </c>
       <c r="N73" t="n">
-        <v>991.502920664279</v>
+        <v>923.6171812794349</v>
       </c>
       <c r="O73" t="n">
-        <v>1277.014264101705</v>
+        <v>1462.308837660917</v>
       </c>
       <c r="P73" t="n">
-        <v>12.63282927928568</v>
+        <v>1270.187828404202</v>
       </c>
       <c r="Q73" t="n">
-        <v>110.8883361816406</v>
+        <v>118.0050659179688</v>
       </c>
       <c r="R73" t="n">
-        <v>357.3987731933594</v>
+        <v>94.43967437744141</v>
       </c>
       <c r="S73" t="n">
-        <v>2.607940446650124</v>
+        <v>7.141772151898734</v>
       </c>
       <c r="T73" t="n">
-        <v>12.34288787841797</v>
+        <v>5.820903778076172</v>
       </c>
       <c r="U73" t="n">
-        <v>16.27472686767578</v>
+        <v>5.578895568847656</v>
       </c>
       <c r="V73" t="n">
-        <v>12.7014045715332</v>
+        <v>5.595939636230469</v>
       </c>
       <c r="W73" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="X73" t="n">
-        <v>1.427830104531529</v>
+        <v>0.5392013898492887</v>
       </c>
       <c r="Y73" t="n">
         <v>1</v>
@@ -7260,19 +7474,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA73" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AB73" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC73" t="b">
+        <v>7</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6_stack4-5</t>
+          <t>6_stackf1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7281,70 +7498,70 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D74" t="b">
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F74" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G74" t="n">
-        <v>17.76611936501783</v>
+        <v>32.58490622819851</v>
       </c>
       <c r="H74" t="n">
-        <v>4.756104049747635</v>
+        <v>6.441148280487683</v>
       </c>
       <c r="I74" t="n">
-        <v>0.03221758669323236</v>
+        <v>0.04530072702485366</v>
       </c>
       <c r="J74" t="n">
-        <v>0.9455642173546173</v>
+        <v>0.3082618953914096</v>
       </c>
       <c r="K74" t="n">
-        <v>16.59496898175367</v>
+        <v>33.37846098381075</v>
       </c>
       <c r="L74" t="n">
-        <v>5.985586378881651</v>
+        <v>7.702503568942353</v>
       </c>
       <c r="M74" t="n">
-        <v>3.426557963852115</v>
+        <v>4.42408727523893</v>
       </c>
       <c r="N74" t="n">
-        <v>551.4416562041808</v>
+        <v>719.3020591109105</v>
       </c>
       <c r="O74" t="n">
-        <v>768.2094103033942</v>
+        <v>909.7598700538996</v>
       </c>
       <c r="P74" t="n">
-        <v>547.1348979158947</v>
+        <v>794.2989490323538</v>
       </c>
       <c r="Q74" t="n">
-        <v>86.65517425537109</v>
+        <v>123.7346954345703</v>
       </c>
       <c r="R74" t="n">
-        <v>515.200439453125</v>
+        <v>96.28834533691406</v>
       </c>
       <c r="S74" t="n">
-        <v>5.482758620689655</v>
+        <v>8.595238095238095</v>
       </c>
       <c r="T74" t="n">
-        <v>10.10122680664062</v>
+        <v>3.591472625732422</v>
       </c>
       <c r="U74" t="n">
-        <v>10.6827507019043</v>
+        <v>11.65071868896484</v>
       </c>
       <c r="V74" t="n">
-        <v>10.65617752075195</v>
+        <v>11.06863403320312</v>
       </c>
       <c r="W74" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="X74" t="n">
-        <v>1.197915630328209</v>
+        <v>1.066527382782237</v>
       </c>
       <c r="Y74" t="n">
         <v>1</v>
@@ -7353,12 +7570,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA74" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AB74" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC74" t="b">
+        <v>7</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7374,70 +7594,70 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D75" t="b">
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F75" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G75" t="n">
-        <v>167.1401132153021</v>
+        <v>28.59621781696019</v>
       </c>
       <c r="H75" t="n">
-        <v>14.58798826628383</v>
+        <v>6.034056293606644</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1992278605220627</v>
+        <v>0.04033350141984453</v>
       </c>
       <c r="J75" t="n">
-        <v>1.043842058003434</v>
+        <v>1.700403243108774</v>
       </c>
       <c r="K75" t="n">
-        <v>176.507353532041</v>
+        <v>25.50437496566868</v>
       </c>
       <c r="L75" t="n">
-        <v>11.62357420611151</v>
+        <v>9.303180074604064</v>
       </c>
       <c r="M75" t="n">
-        <v>7.18897125571193</v>
+        <v>4.92367716253464</v>
       </c>
       <c r="N75" t="n">
-        <v>838.9394574499926</v>
+        <v>708.994181271119</v>
       </c>
       <c r="O75" t="n">
-        <v>1023.219939233074</v>
+        <v>900.1087023436379</v>
       </c>
       <c r="P75" t="n">
-        <v>168.0715547591921</v>
+        <v>1125.616474695607</v>
       </c>
       <c r="Q75" t="n">
-        <v>111.0864562988281</v>
+        <v>51.26511764526367</v>
       </c>
       <c r="R75" t="n">
-        <v>585.07568359375</v>
+        <v>151.2331237792969</v>
       </c>
       <c r="S75" t="n">
-        <v>5.408006814310051</v>
+        <v>7.4</v>
       </c>
       <c r="T75" t="n">
-        <v>10.11078643798828</v>
+        <v>23.88432693481445</v>
       </c>
       <c r="U75" t="n">
-        <v>9.686126708984375</v>
+        <v>14.04627227783203</v>
       </c>
       <c r="V75" t="n">
-        <v>9.986000061035156</v>
+        <v>14.44477462768555</v>
       </c>
       <c r="W75" t="n">
         <v>30</v>
       </c>
       <c r="X75" t="n">
-        <v>0.962209291373328</v>
+        <v>1.391838200841345</v>
       </c>
       <c r="Y75" t="n">
         <v>1</v>
@@ -7446,13 +7666,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA75" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AB75" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC75" t="b">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -7467,70 +7690,70 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D76" t="b">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
         <v>25</v>
       </c>
       <c r="G76" t="n">
-        <v>153.5978274596082</v>
+        <v>26.0000693536171</v>
       </c>
       <c r="H76" t="n">
-        <v>13.98452101099575</v>
+        <v>5.753635065493996</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3125529651860312</v>
+        <v>0.03099159197094614</v>
       </c>
       <c r="J76" t="n">
-        <v>0.9433023469168047</v>
+        <v>2.566047862771189</v>
       </c>
       <c r="K76" t="n">
-        <v>158.2672401114897</v>
+        <v>24.20883415916099</v>
       </c>
       <c r="L76" t="n">
-        <v>11.05414564694251</v>
+        <v>7.223585482600548</v>
       </c>
       <c r="M76" t="n">
-        <v>8.606672446084522</v>
+        <v>3.244354114941592</v>
       </c>
       <c r="N76" t="n">
-        <v>491.429756131691</v>
+        <v>838.9394574499926</v>
       </c>
       <c r="O76" t="n">
-        <v>411.3123669690406</v>
+        <v>1023.219939233074</v>
       </c>
       <c r="P76" t="n">
-        <v>185.294573559212</v>
+        <v>221.4668362781605</v>
       </c>
       <c r="Q76" t="n">
-        <v>97.21729278564453</v>
+        <v>75.35611724853516</v>
       </c>
       <c r="R76" t="n">
-        <v>813.7872924804688</v>
+        <v>585.07568359375</v>
       </c>
       <c r="S76" t="n">
-        <v>6.528621495327103</v>
+        <v>8.967625899280575</v>
       </c>
       <c r="T76" t="n">
-        <v>13.83789825439453</v>
+        <v>14.46254348754883</v>
       </c>
       <c r="U76" t="n">
-        <v>14.66963195800781</v>
+        <v>5.636116027832031</v>
       </c>
       <c r="V76" t="n">
-        <v>14.19779968261719</v>
+        <v>6.638008117675781</v>
       </c>
       <c r="W76" t="n">
         <v>30</v>
       </c>
       <c r="X76" t="n">
-        <v>1.368040725833463</v>
+        <v>0.6396107598638564</v>
       </c>
       <c r="Y76" t="n">
         <v>1</v>
@@ -7539,12 +7762,15 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA76" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AB76" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC76" t="b">
+        <v>7</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7560,70 +7786,70 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D77" t="b">
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F77" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G77" t="n">
-        <v>120.5582618695273</v>
+        <v>18.34276509857201</v>
       </c>
       <c r="H77" t="n">
-        <v>12.38949338983719</v>
+        <v>4.832673575081381</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1150591367384773</v>
+        <v>0.0131441822859669</v>
       </c>
       <c r="J77" t="n">
-        <v>1.034337687857007</v>
+        <v>2.145487000062139</v>
       </c>
       <c r="K77" t="n">
-        <v>116.4015465638115</v>
+        <v>19.91722590090136</v>
       </c>
       <c r="L77" t="n">
-        <v>13.40390185384491</v>
+        <v>5.335858182432136</v>
       </c>
       <c r="M77" t="n">
-        <v>10.53782197871894</v>
+        <v>4.462398476148767</v>
       </c>
       <c r="N77" t="n">
-        <v>1047.793902222204</v>
+        <v>1395.504467261935</v>
       </c>
       <c r="O77" t="n">
-        <v>1370.62274441343</v>
+        <v>1368.30803345853</v>
       </c>
       <c r="P77" t="n">
-        <v>1125.616474695607</v>
+        <v>416.7264366601631</v>
       </c>
       <c r="Q77" t="n">
-        <v>77.28485107421875</v>
+        <v>58.18367385864258</v>
       </c>
       <c r="R77" t="n">
-        <v>477</v>
+        <v>151.3169708251953</v>
       </c>
       <c r="S77" t="n">
-        <v>6.942667471333736</v>
+        <v>3.299319727891156</v>
       </c>
       <c r="T77" t="n">
-        <v>14.86717987060547</v>
+        <v>28.8447380065918</v>
       </c>
       <c r="U77" t="n">
-        <v>14.37362289428711</v>
+        <v>13.44437789916992</v>
       </c>
       <c r="V77" t="n">
-        <v>14.44396591186523</v>
+        <v>14.50589370727539</v>
       </c>
       <c r="W77" t="n">
         <v>30</v>
       </c>
       <c r="X77" t="n">
-        <v>1.391760276359909</v>
+        <v>1.397727380282772</v>
       </c>
       <c r="Y77" t="n">
         <v>1</v>
@@ -7632,19 +7858,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA77" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AB77" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC77" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6_stackf1</t>
+          <t>6_stackf2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7653,70 +7882,70 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D78" t="b">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F78" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G78" t="n">
-        <v>114.9422092400107</v>
+        <v>39.11456196754072</v>
       </c>
       <c r="H78" t="n">
-        <v>12.09747767774775</v>
+        <v>7.057067880647518</v>
       </c>
       <c r="I78" t="n">
-        <v>0.08236606326709535</v>
+        <v>0.04860638216047711</v>
       </c>
       <c r="J78" t="n">
-        <v>1.186249715813747</v>
+        <v>1.028227605608021</v>
       </c>
       <c r="K78" t="n">
-        <v>90.41770624039185</v>
+        <v>36.47869168735927</v>
       </c>
       <c r="L78" t="n">
-        <v>13.52283253157171</v>
+        <v>7.900305825544088</v>
       </c>
       <c r="M78" t="n">
-        <v>12.26630963487948</v>
+        <v>6.462862042830143</v>
       </c>
       <c r="N78" t="n">
-        <v>1395.504467261935</v>
+        <v>804.7207018700027</v>
       </c>
       <c r="O78" t="n">
-        <v>1368.30803345853</v>
+        <v>1125.655707084673</v>
       </c>
       <c r="P78" t="n">
-        <v>1125.616474695607</v>
+        <v>560.1992834749076</v>
       </c>
       <c r="Q78" t="n">
-        <v>68.08979797363281</v>
+        <v>87.60932922363281</v>
       </c>
       <c r="R78" t="n">
-        <v>151.3169708251953</v>
+        <v>473.5828247070312</v>
       </c>
       <c r="S78" t="n">
-        <v>6.123265306122449</v>
+        <v>3.918367346938775</v>
       </c>
       <c r="T78" t="n">
-        <v>16.71946716308594</v>
+        <v>12.34229278564453</v>
       </c>
       <c r="U78" t="n">
-        <v>14.09439086914062</v>
+        <v>12.00346374511719</v>
       </c>
       <c r="V78" t="n">
-        <v>14.43611907958984</v>
+        <v>12.03810882568359</v>
       </c>
       <c r="W78" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X78" t="n">
-        <v>1.391004188348985</v>
+        <v>1.159941927882914</v>
       </c>
       <c r="Y78" t="n">
         <v>1</v>
@@ -7725,19 +7954,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA78" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB78" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC78" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6_stackf1</t>
+          <t>6_stackf2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7746,70 +7978,70 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D79" t="b">
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F79" t="n">
         <v>20</v>
       </c>
       <c r="G79" t="n">
-        <v>52.38768966104699</v>
+        <v>34.49745952685657</v>
       </c>
       <c r="H79" t="n">
-        <v>8.167134022027462</v>
+        <v>6.627482905484899</v>
       </c>
       <c r="I79" t="n">
-        <v>0.04999808602621283</v>
+        <v>0.03306782643328871</v>
       </c>
       <c r="J79" t="n">
-        <v>1.74111121966838</v>
+        <v>1.267746164146205</v>
       </c>
       <c r="K79" t="n">
-        <v>55.42482231449618</v>
+        <v>33.50570680729296</v>
       </c>
       <c r="L79" t="n">
-        <v>7.580602160149171</v>
+        <v>9.108328987434287</v>
       </c>
       <c r="M79" t="n">
-        <v>6.355574860925138</v>
+        <v>5.25253571410531</v>
       </c>
       <c r="N79" t="n">
-        <v>1047.793902222204</v>
+        <v>1043.233355432418</v>
       </c>
       <c r="O79" t="n">
-        <v>1370.62274441343</v>
+        <v>1447.910550873656</v>
       </c>
       <c r="P79" t="n">
-        <v>416.7264366601631</v>
+        <v>747.4554764874249</v>
       </c>
       <c r="Q79" t="n">
-        <v>74.39968872070312</v>
+        <v>94.24842834472656</v>
       </c>
       <c r="R79" t="n">
-        <v>477</v>
+        <v>478.6318969726562</v>
       </c>
       <c r="S79" t="n">
-        <v>4.537037037037037</v>
+        <v>4.317610062893082</v>
       </c>
       <c r="T79" t="n">
-        <v>22.5695686340332</v>
+        <v>13.41379165649414</v>
       </c>
       <c r="U79" t="n">
-        <v>12.96273803710938</v>
+        <v>10.58081817626953</v>
       </c>
       <c r="V79" t="n">
-        <v>14.50303649902344</v>
+        <v>10.81037521362305</v>
       </c>
       <c r="W79" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X79" t="n">
-        <v>1.397452071619582</v>
+        <v>1.041642640717324</v>
       </c>
       <c r="Y79" t="n">
         <v>1</v>
@@ -7818,19 +8050,22 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA79" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB79" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC79" t="b">
+        <v>4</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6_stackf1</t>
+          <t>6_stackf2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7839,70 +8074,70 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D80" t="b">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G80" t="n">
-        <v>44.23710646893255</v>
+        <v>30.37982522630797</v>
       </c>
       <c r="H80" t="n">
-        <v>7.504960579570328</v>
+        <v>6.219388622708681</v>
       </c>
       <c r="I80" t="n">
-        <v>0.04789549974336052</v>
+        <v>0.0291208338653202</v>
       </c>
       <c r="J80" t="n">
-        <v>1.043379232724821</v>
+        <v>0.6976208491816432</v>
       </c>
       <c r="K80" t="n">
-        <v>43.80161452731908</v>
+        <v>29.21895577547742</v>
       </c>
       <c r="L80" t="n">
-        <v>8.341678666274161</v>
+        <v>7.100445144192907</v>
       </c>
       <c r="M80" t="n">
-        <v>6.116589750012188</v>
+        <v>4.301255555111517</v>
       </c>
       <c r="N80" t="n">
-        <v>923.6171812794349</v>
+        <v>1043.233355432418</v>
       </c>
       <c r="O80" t="n">
-        <v>1462.308837660917</v>
+        <v>1447.910550873656</v>
       </c>
       <c r="P80" t="n">
-        <v>1270.187828404202</v>
+        <v>572.7536479760611</v>
       </c>
       <c r="Q80" t="n">
-        <v>118.0050659179688</v>
+        <v>87.53284454345703</v>
       </c>
       <c r="R80" t="n">
-        <v>94.43967437744141</v>
+        <v>478.6318969726562</v>
       </c>
       <c r="S80" t="n">
-        <v>7.141772151898734</v>
+        <v>4.313868613138686</v>
       </c>
       <c r="T80" t="n">
-        <v>5.820903778076172</v>
+        <v>10.48086547851562</v>
       </c>
       <c r="U80" t="n">
-        <v>5.578895568847656</v>
+        <v>15.02372741699219</v>
       </c>
       <c r="V80" t="n">
-        <v>5.595939636230469</v>
+        <v>14.67743682861328</v>
       </c>
       <c r="W80" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X80" t="n">
-        <v>0.5392013898492887</v>
+        <v>1.414256559555117</v>
       </c>
       <c r="Y80" t="n">
         <v>1</v>
@@ -7911,385 +8146,16 @@
         <v>0.1980716765873016</v>
       </c>
       <c r="AA80" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB80" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC80" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>6_stackf1</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>7</v>
-      </c>
-      <c r="D81" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" t="n">
-        <v>18</v>
-      </c>
-      <c r="F81" t="n">
-        <v>24</v>
-      </c>
-      <c r="G81" t="n">
-        <v>32.58490622819851</v>
-      </c>
-      <c r="H81" t="n">
-        <v>6.441148280487683</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.04530072702485366</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0.3082618953914096</v>
-      </c>
-      <c r="K81" t="n">
-        <v>33.37846098381075</v>
-      </c>
-      <c r="L81" t="n">
-        <v>7.702503568942353</v>
-      </c>
-      <c r="M81" t="n">
-        <v>4.42408727523893</v>
-      </c>
-      <c r="N81" t="n">
-        <v>719.3020591109105</v>
-      </c>
-      <c r="O81" t="n">
-        <v>909.7598700538996</v>
-      </c>
-      <c r="P81" t="n">
-        <v>794.2989490323538</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>123.7346954345703</v>
-      </c>
-      <c r="R81" t="n">
-        <v>96.28834533691406</v>
-      </c>
-      <c r="S81" t="n">
-        <v>8.595238095238095</v>
-      </c>
-      <c r="T81" t="n">
-        <v>3.591472625732422</v>
-      </c>
-      <c r="U81" t="n">
-        <v>11.65071868896484</v>
-      </c>
-      <c r="V81" t="n">
-        <v>11.06863403320312</v>
-      </c>
-      <c r="W81" t="n">
-        <v>30</v>
-      </c>
-      <c r="X81" t="n">
-        <v>1.066527382782237</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>0.1980716765873016</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>6_stackf1</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>8</v>
-      </c>
-      <c r="D82" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" t="n">
-        <v>13</v>
-      </c>
-      <c r="F82" t="n">
-        <v>21</v>
-      </c>
-      <c r="G82" t="n">
-        <v>28.59621781696019</v>
-      </c>
-      <c r="H82" t="n">
-        <v>6.034056293606644</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.04033350141984453</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1.700403243108774</v>
-      </c>
-      <c r="K82" t="n">
-        <v>25.50437496566868</v>
-      </c>
-      <c r="L82" t="n">
-        <v>9.303180074604064</v>
-      </c>
-      <c r="M82" t="n">
-        <v>4.92367716253464</v>
-      </c>
-      <c r="N82" t="n">
-        <v>708.994181271119</v>
-      </c>
-      <c r="O82" t="n">
-        <v>900.1087023436379</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1125.616474695607</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>51.26511764526367</v>
-      </c>
-      <c r="R82" t="n">
-        <v>151.2331237792969</v>
-      </c>
-      <c r="S82" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="T82" t="n">
-        <v>23.88432693481445</v>
-      </c>
-      <c r="U82" t="n">
-        <v>14.04627227783203</v>
-      </c>
-      <c r="V82" t="n">
-        <v>14.44477462768555</v>
-      </c>
-      <c r="W82" t="n">
-        <v>30</v>
-      </c>
-      <c r="X82" t="n">
-        <v>1.391838200841345</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0.1980716765873016</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC82" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>6_stackf1</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>9</v>
-      </c>
-      <c r="D83" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
         <v>4</v>
       </c>
-      <c r="F83" t="n">
-        <v>22</v>
-      </c>
-      <c r="G83" t="n">
-        <v>26.0000693536171</v>
-      </c>
-      <c r="H83" t="n">
-        <v>5.753635065493996</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.03099159197094614</v>
-      </c>
-      <c r="J83" t="n">
-        <v>2.566047862771189</v>
-      </c>
-      <c r="K83" t="n">
-        <v>24.20883415916099</v>
-      </c>
-      <c r="L83" t="n">
-        <v>7.223585482600548</v>
-      </c>
-      <c r="M83" t="n">
-        <v>3.244354114941592</v>
-      </c>
-      <c r="N83" t="n">
-        <v>838.9394574499926</v>
-      </c>
-      <c r="O83" t="n">
-        <v>1023.219939233074</v>
-      </c>
-      <c r="P83" t="n">
-        <v>221.4668362781605</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>75.35611724853516</v>
-      </c>
-      <c r="R83" t="n">
-        <v>585.07568359375</v>
-      </c>
-      <c r="S83" t="n">
-        <v>8.967625899280575</v>
-      </c>
-      <c r="T83" t="n">
-        <v>14.46254348754883</v>
-      </c>
-      <c r="U83" t="n">
-        <v>5.636116027832031</v>
-      </c>
-      <c r="V83" t="n">
-        <v>6.638008117675781</v>
-      </c>
-      <c r="W83" t="n">
-        <v>30</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0.6396107598638564</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>0.1980716765873016</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>6_stackf1</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>10</v>
-      </c>
-      <c r="D84" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" t="n">
-        <v>15</v>
-      </c>
-      <c r="F84" t="n">
-        <v>20</v>
-      </c>
-      <c r="G84" t="n">
-        <v>18.34276509857201</v>
-      </c>
-      <c r="H84" t="n">
-        <v>4.832673575081381</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.0131441822859669</v>
-      </c>
-      <c r="J84" t="n">
-        <v>2.145487000062139</v>
-      </c>
-      <c r="K84" t="n">
-        <v>19.91722590090136</v>
-      </c>
-      <c r="L84" t="n">
-        <v>5.335858182432136</v>
-      </c>
-      <c r="M84" t="n">
-        <v>4.462398476148767</v>
-      </c>
-      <c r="N84" t="n">
-        <v>1395.504467261935</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1368.30803345853</v>
-      </c>
-      <c r="P84" t="n">
-        <v>416.7264366601631</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>58.18367385864258</v>
-      </c>
-      <c r="R84" t="n">
-        <v>151.3169708251953</v>
-      </c>
-      <c r="S84" t="n">
-        <v>3.299319727891156</v>
-      </c>
-      <c r="T84" t="n">
-        <v>28.8447380065918</v>
-      </c>
-      <c r="U84" t="n">
-        <v>13.44437789916992</v>
-      </c>
-      <c r="V84" t="n">
-        <v>14.50589370727539</v>
-      </c>
-      <c r="W84" t="n">
-        <v>30</v>
-      </c>
-      <c r="X84" t="n">
-        <v>1.397727380282772</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>0.1980716765873016</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC84" t="b">
-        <v>0</v>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
